--- a/Laboratorio/esperienza2/esperienza2.xlsx
+++ b/Laboratorio/esperienza2/esperienza2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericm\Desktop\Laboratorio-di-Ottica\Laboratorio\esperienza2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF0CC10-9F3A-4A5D-A86E-FD64897C781F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3D6209-5825-4AE0-97F1-546326BF7395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -175,10 +175,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2255,7 +2254,7 @@
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2283,7 +2282,7 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
     </row>

--- a/Laboratorio/esperienza2/esperienza2.xlsx
+++ b/Laboratorio/esperienza2/esperienza2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericm\Desktop\Laboratorio-di-Ottica\Laboratorio\esperienza2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5AC01E1-6DAD-489A-83F8-778CAEE16694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432B1F78-5D74-471C-8892-CB7002E429AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Laboratorio/esperienza2/esperienza2.xlsx
+++ b/Laboratorio/esperienza2/esperienza2.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericm\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michele/Documents/Vscode/Laboratorio-di-Ottica/Laboratorio/esperienza2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{6F145F87-FF90-4AFC-B3DC-073C5EEB0D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815CA4A0-DA42-214E-B823-06ADB09090B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="23260" windowHeight="12460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
-    <sheet name="Dati" sheetId="2" r:id="rId2"/>
-    <sheet name="Dati (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="Datisium" sheetId="2" r:id="rId2"/>
+    <sheet name="Dati" sheetId="4" r:id="rId3"/>
+    <sheet name="Dati (2)" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,10 +46,10 @@
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0" xr:uid="{8F9FD4D8-9329-4419-88E1-4D29327B2685}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Inserire qui finchè non si riesce a misurare y_max, appena si riesce copiare i valori nella colonna y_max e continuare su quella colonna</t>
+        <t>[Commento in thread]
+La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
+Commento:
+Inserire qui finchè non si riesce a misurare y_max, appena si riesce copiare i valori nella colonna y_max e continuare su quella colonna</t>
       </text>
     </comment>
   </commentList>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t xml:space="preserve"> L</t>
   </si>
@@ -237,7 +237,7 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -255,7 +255,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -329,7 +329,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$G$1</c:f>
+              <c:f>Datisium!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -345,7 +345,7 @@
           </c:spPr>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$335</c:f>
+              <c:f>Datisium!$F$2:$F$335</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="334"/>
@@ -702,7 +702,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$335</c:f>
+              <c:f>Datisium!$G$2:$G$335</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="334"/>
@@ -1069,7 +1069,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$G$1</c:f>
+              <c:f>Datisium!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1086,7 +1086,7 @@
           </c:spPr>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$335</c:f>
+              <c:f>Datisium!$F$2:$F$335</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="334"/>
@@ -1443,7 +1443,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$335</c:f>
+              <c:f>Datisium!$G$2:$G$335</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="334"/>
@@ -1810,7 +1810,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$G$1</c:f>
+              <c:f>Datisium!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1826,7 +1826,7 @@
           </c:spPr>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$335</c:f>
+              <c:f>Datisium!$F$2:$F$335</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="334"/>
@@ -2183,7 +2183,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$335</c:f>
+              <c:f>Datisium!$G$2:$G$335</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="334"/>
@@ -2550,7 +2550,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$G$1</c:f>
+              <c:f>Datisium!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2567,7 +2567,7 @@
           </c:spPr>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$335</c:f>
+              <c:f>Datisium!$F$2:$F$335</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="334"/>
@@ -2924,7 +2924,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$335</c:f>
+              <c:f>Datisium!$G$2:$G$335</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="334"/>
@@ -3291,7 +3291,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$G$1</c:f>
+              <c:f>Datisium!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3307,7 +3307,7 @@
           </c:spPr>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$335</c:f>
+              <c:f>Datisium!$F$2:$F$335</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="334"/>
@@ -3664,7 +3664,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$335</c:f>
+              <c:f>Datisium!$G$2:$G$335</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="334"/>
@@ -4031,7 +4031,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$G$1</c:f>
+              <c:f>Datisium!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4048,7 +4048,7 @@
           </c:spPr>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$335</c:f>
+              <c:f>Datisium!$F$2:$F$335</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="334"/>
@@ -4405,7 +4405,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$335</c:f>
+              <c:f>Datisium!$G$2:$G$335</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="334"/>
@@ -4772,7 +4772,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$G$1</c:f>
+              <c:f>Datisium!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4788,7 +4788,7 @@
           </c:spPr>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$335</c:f>
+              <c:f>Datisium!$F$2:$F$335</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="334"/>
@@ -5145,7 +5145,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$335</c:f>
+              <c:f>Datisium!$G$2:$G$335</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="334"/>
@@ -5512,7 +5512,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$G$1</c:f>
+              <c:f>Datisium!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5544,7 +5544,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$335</c:f>
+              <c:f>Datisium!$F$2:$F$335</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="334"/>
@@ -5901,7 +5901,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$G$2:$G$335</c:f>
+              <c:f>Datisium!$G$2:$G$335</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="334"/>
@@ -6292,7 +6292,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Dati!$U$2:$U$3</c15:sqref>
+                          <c15:sqref>Datisium!$U$2:$U$3</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -6313,7 +6313,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Dati!$V$2:$V$3</c15:sqref>
+                          <c15:sqref>Datisium!$V$2:$V$3</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -6562,7 +6562,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6643,7 +6643,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dati!$F$1</c:f>
+              <c:f>Datisium!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6676,7 +6676,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$121</c:f>
+              <c:f>Datisium!$F$2:$F$121</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="120"/>
@@ -7033,7 +7033,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$B$2:$B$121</c:f>
+              <c:f>Datisium!$B$2:$B$121</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="120"/>
@@ -7585,7 +7585,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7688,7 +7688,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$67</c:f>
+              <c:f>Datisium!$F$2:$F$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="66"/>
@@ -7895,7 +7895,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$B$2:$B$67</c:f>
+              <c:f>Datisium!$B$2:$B$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="66"/>
@@ -8137,7 +8137,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$117</c:f>
+              <c:f>Datisium!$F$2:$F$117</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="116"/>
@@ -8494,7 +8494,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$C$2:$C$117</c:f>
+              <c:f>Datisium!$C$2:$C$117</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="116"/>
@@ -8718,7 +8718,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$F$2:$F$117</c:f>
+              <c:f>Datisium!$F$2:$F$117</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="116"/>
@@ -9075,7 +9075,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$D$2:$D$83</c:f>
+              <c:f>Datisium!$D$2:$D$83</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="82"/>
@@ -9525,7 +9525,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16158,7 +16158,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -20099,9 +20099,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20112,7 +20112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>104</v>
       </c>
@@ -20125,7 +20125,7 @@
         <v>2.8867513459481291E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -20136,7 +20136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>17</v>
       </c>
@@ -20149,7 +20149,7 @@
         <v>2.8867513459481291E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -20163,7 +20163,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>237</v>
       </c>
@@ -20179,7 +20179,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>131</v>
       </c>
@@ -20217,12 +20217,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2111728D-DB7A-48AC-96F2-90D17D913CED}">
   <dimension ref="A1:V117"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -20251,7 +20251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>251</v>
       </c>
@@ -20299,7 +20299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>252</v>
@@ -20348,7 +20348,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A35" si="3">A3+1</f>
         <v>253</v>
@@ -20388,7 +20388,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -20428,7 +20428,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -20468,7 +20468,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -20508,7 +20508,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -20548,7 +20548,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -20588,7 +20588,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -20628,7 +20628,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -20668,7 +20668,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <f t="shared" si="3"/>
         <v>261</v>
@@ -20708,7 +20708,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <f t="shared" si="3"/>
         <v>262</v>
@@ -20748,7 +20748,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <f t="shared" si="3"/>
         <v>263</v>
@@ -20788,7 +20788,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <f t="shared" si="3"/>
         <v>264</v>
@@ -20828,7 +20828,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <f t="shared" si="3"/>
         <v>265</v>
@@ -20868,7 +20868,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <f t="shared" si="3"/>
         <v>266</v>
@@ -20908,7 +20908,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <f t="shared" si="3"/>
         <v>267</v>
@@ -20948,7 +20948,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <f t="shared" si="3"/>
         <v>268</v>
@@ -20988,7 +20988,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <f t="shared" si="3"/>
         <v>269</v>
@@ -21028,7 +21028,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <f t="shared" si="3"/>
         <v>270</v>
@@ -21068,7 +21068,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <f t="shared" si="3"/>
         <v>271</v>
@@ -21108,7 +21108,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <f t="shared" si="3"/>
         <v>272</v>
@@ -21148,7 +21148,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <f t="shared" si="3"/>
         <v>273</v>
@@ -21188,7 +21188,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <f t="shared" si="3"/>
         <v>274</v>
@@ -21228,7 +21228,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <f t="shared" si="3"/>
         <v>275</v>
@@ -21268,7 +21268,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <f t="shared" si="3"/>
         <v>276</v>
@@ -21308,7 +21308,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <f t="shared" si="3"/>
         <v>277</v>
@@ -21348,7 +21348,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <f t="shared" si="3"/>
         <v>278</v>
@@ -21388,7 +21388,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <f t="shared" si="3"/>
         <v>279</v>
@@ -21428,7 +21428,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <f t="shared" si="3"/>
         <v>280</v>
@@ -21468,7 +21468,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <f t="shared" si="3"/>
         <v>281</v>
@@ -21508,7 +21508,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <f t="shared" si="3"/>
         <v>282</v>
@@ -21548,7 +21548,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <f t="shared" si="3"/>
         <v>283</v>
@@ -21588,7 +21588,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <f t="shared" si="3"/>
         <v>284</v>
@@ -21628,7 +21628,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <f>A35+2</f>
         <v>286</v>
@@ -21668,7 +21668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <f t="shared" ref="A37:A41" si="4">A36+2</f>
         <v>288</v>
@@ -21708,7 +21708,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <f t="shared" si="4"/>
         <v>290</v>
@@ -21748,7 +21748,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -21788,7 +21788,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <f t="shared" si="4"/>
         <v>294</v>
@@ -21828,7 +21828,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <f t="shared" si="4"/>
         <v>296</v>
@@ -21868,7 +21868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <f>A41+3</f>
         <v>299</v>
@@ -21908,7 +21908,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <f>A42+1</f>
         <v>300</v>
@@ -21948,7 +21948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <f t="shared" ref="A44:A57" si="5">A43+1</f>
         <v>301</v>
@@ -21988,7 +21988,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <f t="shared" si="5"/>
         <v>302</v>
@@ -22028,7 +22028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <f t="shared" si="5"/>
         <v>303</v>
@@ -22071,7 +22071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <f>A46+1</f>
         <v>304</v>
@@ -22111,7 +22111,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <f t="shared" si="5"/>
         <v>305</v>
@@ -22151,7 +22151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <f t="shared" si="5"/>
         <v>306</v>
@@ -22191,7 +22191,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <f t="shared" si="5"/>
         <v>307</v>
@@ -22231,7 +22231,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <f t="shared" si="5"/>
         <v>308</v>
@@ -22271,7 +22271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <f t="shared" si="5"/>
         <v>309</v>
@@ -22311,7 +22311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <f t="shared" si="5"/>
         <v>310</v>
@@ -22351,7 +22351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <f t="shared" si="5"/>
         <v>311</v>
@@ -22391,7 +22391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <f t="shared" si="5"/>
         <v>312</v>
@@ -22431,7 +22431,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <f t="shared" si="5"/>
         <v>313</v>
@@ -22471,7 +22471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <f t="shared" si="5"/>
         <v>314</v>
@@ -22511,7 +22511,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <f>A57+2</f>
         <v>316</v>
@@ -22551,7 +22551,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <f t="shared" ref="A59:A60" si="6">A58+2</f>
         <v>318</v>
@@ -22591,7 +22591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <f t="shared" si="6"/>
         <v>320</v>
@@ -22631,7 +22631,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <f>A60+5</f>
         <v>325</v>
@@ -22671,7 +22671,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <f t="shared" ref="A62:A86" si="7">A61+5</f>
         <v>330</v>
@@ -22711,7 +22711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="11">
         <f t="shared" si="7"/>
         <v>335</v>
@@ -22751,7 +22751,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <f t="shared" si="7"/>
         <v>340</v>
@@ -22788,7 +22788,7 @@
         <v>-871</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <f t="shared" si="7"/>
         <v>345</v>
@@ -22825,7 +22825,7 @@
         <v>-870</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <f t="shared" si="7"/>
         <v>350</v>
@@ -22862,7 +22862,7 @@
         <v>-864</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <f t="shared" si="7"/>
         <v>355</v>
@@ -22899,7 +22899,7 @@
         <v>-856</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <f t="shared" si="7"/>
         <v>360</v>
@@ -22936,7 +22936,7 @@
         <v>-851</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <f t="shared" si="7"/>
         <v>365</v>
@@ -22973,7 +22973,7 @@
         <v>-846</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <f t="shared" si="7"/>
         <v>370</v>
@@ -23010,7 +23010,7 @@
         <v>-840</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <f t="shared" si="7"/>
         <v>375</v>
@@ -23047,7 +23047,7 @@
         <v>-835</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <f t="shared" si="7"/>
         <v>380</v>
@@ -23084,7 +23084,7 @@
         <v>-833</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <f t="shared" si="7"/>
         <v>385</v>
@@ -23121,7 +23121,7 @@
         <v>-832</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <f t="shared" si="7"/>
         <v>390</v>
@@ -23158,7 +23158,7 @@
         <v>-828</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <f t="shared" si="7"/>
         <v>395</v>
@@ -23195,7 +23195,7 @@
         <v>-825</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <f t="shared" si="7"/>
         <v>400</v>
@@ -23232,7 +23232,7 @@
         <v>-822</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <f t="shared" si="7"/>
         <v>405</v>
@@ -23269,7 +23269,7 @@
         <v>-820</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <f t="shared" si="7"/>
         <v>410</v>
@@ -23306,7 +23306,7 @@
         <v>-816</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <f t="shared" si="7"/>
         <v>415</v>
@@ -23343,7 +23343,7 @@
         <v>-814</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <f t="shared" si="7"/>
         <v>420</v>
@@ -23380,7 +23380,7 @@
         <v>-822</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <f t="shared" si="7"/>
         <v>425</v>
@@ -23417,7 +23417,7 @@
         <v>-825</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <f t="shared" si="7"/>
         <v>430</v>
@@ -23454,7 +23454,7 @@
         <v>-827</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <f t="shared" si="7"/>
         <v>435</v>
@@ -23491,7 +23491,7 @@
         <v>-827</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <f t="shared" si="7"/>
         <v>440</v>
@@ -23528,7 +23528,7 @@
         <v>-829</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <f t="shared" si="7"/>
         <v>445</v>
@@ -23565,7 +23565,7 @@
         <v>-830</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <f t="shared" si="7"/>
         <v>450</v>
@@ -23602,7 +23602,7 @@
         <v>-831</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <f>A86+10</f>
         <v>460</v>
@@ -23639,7 +23639,7 @@
         <v>-832</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <f t="shared" ref="A88:A101" si="11">A87+10</f>
         <v>470</v>
@@ -23676,7 +23676,7 @@
         <v>-837</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <f t="shared" si="11"/>
         <v>480</v>
@@ -23713,7 +23713,7 @@
         <v>-840</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <f t="shared" si="11"/>
         <v>490</v>
@@ -23750,7 +23750,7 @@
         <v>-835</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <f t="shared" si="11"/>
         <v>500</v>
@@ -23787,7 +23787,7 @@
         <v>-850</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <f t="shared" si="11"/>
         <v>510</v>
@@ -23824,7 +23824,7 @@
         <v>-855</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <f t="shared" si="11"/>
         <v>520</v>
@@ -23861,7 +23861,7 @@
         <v>-860</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <f t="shared" si="11"/>
         <v>530</v>
@@ -23898,7 +23898,7 @@
         <v>-865</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <f t="shared" si="11"/>
         <v>540</v>
@@ -23935,7 +23935,7 @@
         <v>-870</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <f t="shared" si="11"/>
         <v>550</v>
@@ -23972,7 +23972,7 @@
         <v>-875</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <f t="shared" si="11"/>
         <v>560</v>
@@ -24009,7 +24009,7 @@
         <v>-885</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <f t="shared" si="11"/>
         <v>570</v>
@@ -24046,7 +24046,7 @@
         <v>-890</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <f t="shared" si="11"/>
         <v>580</v>
@@ -24083,7 +24083,7 @@
         <v>-897</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <f t="shared" si="11"/>
         <v>590</v>
@@ -24120,7 +24120,7 @@
         <v>-905</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <f t="shared" si="11"/>
         <v>600</v>
@@ -24157,7 +24157,7 @@
         <v>-910</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <f>A101+20</f>
         <v>620</v>
@@ -24194,7 +24194,7 @@
         <v>-925</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <f t="shared" ref="A103:A105" si="12">A102+20</f>
         <v>640</v>
@@ -24231,7 +24231,7 @@
         <v>-939</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <f t="shared" si="12"/>
         <v>660</v>
@@ -24268,7 +24268,7 @@
         <v>-958</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <f t="shared" si="12"/>
         <v>680</v>
@@ -24305,7 +24305,7 @@
         <v>-972</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <f>A105+20</f>
         <v>700</v>
@@ -24342,7 +24342,7 @@
         <v>-990</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <f>A106+50</f>
         <v>750</v>
@@ -24379,7 +24379,7 @@
         <v>-1030</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <f t="shared" ref="A108:A110" si="13">A107+50</f>
         <v>800</v>
@@ -24416,7 +24416,7 @@
         <v>-1073</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <f>A108+50</f>
         <v>850</v>
@@ -24453,7 +24453,7 @@
         <v>-1118</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <f t="shared" si="13"/>
         <v>900</v>
@@ -24490,7 +24490,7 @@
         <v>-1164</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <f>A110+100</f>
         <v>1000</v>
@@ -24527,7 +24527,7 @@
         <v>-1255</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <f t="shared" ref="A112:A116" si="14">A111+100</f>
         <v>1100</v>
@@ -24564,7 +24564,7 @@
         <v>-1349</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <f t="shared" si="14"/>
         <v>1200</v>
@@ -24601,7 +24601,7 @@
         <v>-1445</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <f>A113+100</f>
         <v>1300</v>
@@ -24638,7 +24638,7 @@
         <v>-1542</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <f t="shared" si="14"/>
         <v>1400</v>
@@ -24675,7 +24675,7 @@
         <v>-1638</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <f t="shared" si="14"/>
         <v>1500</v>
@@ -24712,7 +24712,7 @@
         <v>-1736</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>1650</v>
       </c>
@@ -24758,11 +24758,3621 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B143064A-87E3-4C4C-B4A5-A1EDA6B05300}">
+  <dimension ref="A1:V117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>251</v>
+      </c>
+      <c r="B2">
+        <v>1802</v>
+      </c>
+      <c r="C2">
+        <v>1841</v>
+      </c>
+      <c r="D2">
+        <v>1821.3956187495346</v>
+      </c>
+      <c r="E2">
+        <v>11.258330249197703</v>
+      </c>
+      <c r="F2">
+        <v>232.5</v>
+      </c>
+      <c r="G2">
+        <v>1568.3956187495346</v>
+      </c>
+      <c r="H2">
+        <v>11.258330249197703</v>
+      </c>
+      <c r="I2">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K2">
+        <v>39</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>252</v>
+      </c>
+      <c r="B3">
+        <v>1719</v>
+      </c>
+      <c r="C3">
+        <v>1836</v>
+      </c>
+      <c r="D3">
+        <v>1776.5370809527169</v>
+      </c>
+      <c r="E3">
+        <v>33.774990747593108</v>
+      </c>
+      <c r="F3">
+        <v>233.5</v>
+      </c>
+      <c r="G3">
+        <v>1522.5370809527169</v>
+      </c>
+      <c r="H3">
+        <v>33.774990747593108</v>
+      </c>
+      <c r="I3">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K3">
+        <v>117</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3">
+        <v>2000</v>
+      </c>
+      <c r="V3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>253</v>
+      </c>
+      <c r="B4">
+        <v>1690</v>
+      </c>
+      <c r="C4">
+        <v>1853</v>
+      </c>
+      <c r="D4">
+        <v>1769.6242539025059</v>
+      </c>
+      <c r="E4">
+        <v>47.0540469389545</v>
+      </c>
+      <c r="F4">
+        <v>234.5</v>
+      </c>
+      <c r="G4">
+        <v>1514.6242539025059</v>
+      </c>
+      <c r="H4">
+        <v>47.0540469389545</v>
+      </c>
+      <c r="I4">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K4">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>254</v>
+      </c>
+      <c r="B5">
+        <v>1630</v>
+      </c>
+      <c r="C5">
+        <v>1782</v>
+      </c>
+      <c r="D5">
+        <v>1704.3063104970304</v>
+      </c>
+      <c r="E5">
+        <v>43.878620458411561</v>
+      </c>
+      <c r="F5">
+        <v>235.5</v>
+      </c>
+      <c r="G5">
+        <v>1448.3063104970304</v>
+      </c>
+      <c r="H5">
+        <v>43.878620458411561</v>
+      </c>
+      <c r="I5">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>255</v>
+      </c>
+      <c r="B6">
+        <v>1605</v>
+      </c>
+      <c r="C6">
+        <v>1745</v>
+      </c>
+      <c r="D6">
+        <v>1673.5366742321485</v>
+      </c>
+      <c r="E6">
+        <v>40.414518843273804</v>
+      </c>
+      <c r="F6">
+        <v>236.5</v>
+      </c>
+      <c r="G6">
+        <v>1416.5366742321485</v>
+      </c>
+      <c r="H6">
+        <v>40.414518843273804</v>
+      </c>
+      <c r="I6">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>256</v>
+      </c>
+      <c r="B7">
+        <v>1574</v>
+      </c>
+      <c r="C7">
+        <v>1710</v>
+      </c>
+      <c r="D7">
+        <v>1640.5913567979078</v>
+      </c>
+      <c r="E7">
+        <v>39.259818304894551</v>
+      </c>
+      <c r="F7">
+        <v>237.5</v>
+      </c>
+      <c r="G7">
+        <v>1382.5913567979078</v>
+      </c>
+      <c r="H7">
+        <v>39.259818304894551</v>
+      </c>
+      <c r="I7">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K7">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>257</v>
+      </c>
+      <c r="B8">
+        <v>1546</v>
+      </c>
+      <c r="C8">
+        <v>1679</v>
+      </c>
+      <c r="D8">
+        <v>1611.1281761548335</v>
+      </c>
+      <c r="E8">
+        <v>38.393792901110118</v>
+      </c>
+      <c r="F8">
+        <v>238.5</v>
+      </c>
+      <c r="G8">
+        <v>1352.1281761548335</v>
+      </c>
+      <c r="H8">
+        <v>38.393792901110118</v>
+      </c>
+      <c r="I8">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K8">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>258</v>
+      </c>
+      <c r="B9">
+        <v>1525</v>
+      </c>
+      <c r="C9">
+        <v>1629</v>
+      </c>
+      <c r="D9">
+        <v>1576.1424428014113</v>
+      </c>
+      <c r="E9">
+        <v>30.02221399786054</v>
+      </c>
+      <c r="F9">
+        <v>239.5</v>
+      </c>
+      <c r="G9">
+        <v>1316.1424428014113</v>
+      </c>
+      <c r="H9">
+        <v>30.02221399786054</v>
+      </c>
+      <c r="I9">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K9">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>259</v>
+      </c>
+      <c r="B10">
+        <v>1505</v>
+      </c>
+      <c r="C10">
+        <v>1603</v>
+      </c>
+      <c r="D10">
+        <v>1553.227285364251</v>
+      </c>
+      <c r="E10">
+        <v>28.290163190291665</v>
+      </c>
+      <c r="F10">
+        <v>240.5</v>
+      </c>
+      <c r="G10">
+        <v>1292.227285364251</v>
+      </c>
+      <c r="H10">
+        <v>28.290163190291665</v>
+      </c>
+      <c r="I10">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>260</v>
+      </c>
+      <c r="B11">
+        <v>1467</v>
+      </c>
+      <c r="C11">
+        <v>1572</v>
+      </c>
+      <c r="D11">
+        <v>1518.5927696390497</v>
+      </c>
+      <c r="E11">
+        <v>30.310889132455355</v>
+      </c>
+      <c r="F11">
+        <v>241.5</v>
+      </c>
+      <c r="G11">
+        <v>1256.5927696390497</v>
+      </c>
+      <c r="H11">
+        <v>30.310889132455355</v>
+      </c>
+      <c r="I11">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K11">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>261</v>
+      </c>
+      <c r="B12">
+        <v>1452</v>
+      </c>
+      <c r="C12">
+        <v>1534</v>
+      </c>
+      <c r="D12">
+        <v>1492.4369333409034</v>
+      </c>
+      <c r="E12">
+        <v>23.671361036774659</v>
+      </c>
+      <c r="F12">
+        <v>242.5</v>
+      </c>
+      <c r="G12">
+        <v>1229.4369333409034</v>
+      </c>
+      <c r="H12">
+        <v>23.671361036774659</v>
+      </c>
+      <c r="I12">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K12">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>262</v>
+      </c>
+      <c r="B13">
+        <v>1442</v>
+      </c>
+      <c r="C13">
+        <v>1520</v>
+      </c>
+      <c r="D13">
+        <v>1480.4864065569802</v>
+      </c>
+      <c r="E13">
+        <v>22.516660498395407</v>
+      </c>
+      <c r="F13">
+        <v>243.5</v>
+      </c>
+      <c r="G13">
+        <v>1216.4864065569802</v>
+      </c>
+      <c r="H13">
+        <v>22.516660498395407</v>
+      </c>
+      <c r="I13">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>263</v>
+      </c>
+      <c r="B14">
+        <v>1402</v>
+      </c>
+      <c r="C14">
+        <v>1485</v>
+      </c>
+      <c r="D14">
+        <v>1442.9033231647918</v>
+      </c>
+      <c r="E14">
+        <v>23.96003617136947</v>
+      </c>
+      <c r="F14">
+        <v>244.5</v>
+      </c>
+      <c r="G14">
+        <v>1177.9033231647918</v>
+      </c>
+      <c r="H14">
+        <v>23.96003617136947</v>
+      </c>
+      <c r="I14">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K14">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>264</v>
+      </c>
+      <c r="B15">
+        <v>1391</v>
+      </c>
+      <c r="C15">
+        <v>1462</v>
+      </c>
+      <c r="D15">
+        <v>1426.0582035807654</v>
+      </c>
+      <c r="E15">
+        <v>20.495934556231717</v>
+      </c>
+      <c r="F15">
+        <v>245.5</v>
+      </c>
+      <c r="G15">
+        <v>1160.0582035807654</v>
+      </c>
+      <c r="H15">
+        <v>20.495934556231717</v>
+      </c>
+      <c r="I15">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>265</v>
+      </c>
+      <c r="B16">
+        <v>1365</v>
+      </c>
+      <c r="C16">
+        <v>1436</v>
+      </c>
+      <c r="D16">
+        <v>1400.0499991071747</v>
+      </c>
+      <c r="E16">
+        <v>20.495934556231717</v>
+      </c>
+      <c r="F16">
+        <v>246.5</v>
+      </c>
+      <c r="G16">
+        <v>1133.0499991071747</v>
+      </c>
+      <c r="H16">
+        <v>20.495934556231717</v>
+      </c>
+      <c r="I16">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K16">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>266</v>
+      </c>
+      <c r="B17">
+        <v>1358</v>
+      </c>
+      <c r="C17">
+        <v>1431</v>
+      </c>
+      <c r="D17">
+        <v>1394.0222379861807</v>
+      </c>
+      <c r="E17">
+        <v>21.073284825421343</v>
+      </c>
+      <c r="F17">
+        <v>247.5</v>
+      </c>
+      <c r="G17">
+        <v>1126.0222379861807</v>
+      </c>
+      <c r="H17">
+        <v>21.073284825421343</v>
+      </c>
+      <c r="I17">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K17">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>267</v>
+      </c>
+      <c r="B18">
+        <v>1346</v>
+      </c>
+      <c r="C18">
+        <v>1406</v>
+      </c>
+      <c r="D18">
+        <v>1375.6729262437348</v>
+      </c>
+      <c r="E18">
+        <v>17.320508075688775</v>
+      </c>
+      <c r="F18">
+        <v>248.5</v>
+      </c>
+      <c r="G18">
+        <v>1106.6729262437348</v>
+      </c>
+      <c r="H18">
+        <v>17.320508075688775</v>
+      </c>
+      <c r="I18">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>268</v>
+      </c>
+      <c r="B19">
+        <v>1323</v>
+      </c>
+      <c r="C19">
+        <v>1390</v>
+      </c>
+      <c r="D19">
+        <v>1356.0862804408871</v>
+      </c>
+      <c r="E19">
+        <v>19.341234017852464</v>
+      </c>
+      <c r="F19">
+        <v>249.5</v>
+      </c>
+      <c r="G19">
+        <v>1086.0862804408871</v>
+      </c>
+      <c r="H19">
+        <v>19.341234017852464</v>
+      </c>
+      <c r="I19">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K19">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>269</v>
+      </c>
+      <c r="B20">
+        <v>1303</v>
+      </c>
+      <c r="C20">
+        <v>1368</v>
+      </c>
+      <c r="D20">
+        <v>1335.1044902928011</v>
+      </c>
+      <c r="E20">
+        <v>18.763883748662838</v>
+      </c>
+      <c r="F20">
+        <v>250.5</v>
+      </c>
+      <c r="G20">
+        <v>1064.1044902928011</v>
+      </c>
+      <c r="H20">
+        <v>18.763883748662838</v>
+      </c>
+      <c r="I20">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>270</v>
+      </c>
+      <c r="B21">
+        <v>1294</v>
+      </c>
+      <c r="C21">
+        <v>1346</v>
+      </c>
+      <c r="D21">
+        <v>1319.7439145531227</v>
+      </c>
+      <c r="E21">
+        <v>15.01110699893027</v>
+      </c>
+      <c r="F21">
+        <v>251.5</v>
+      </c>
+      <c r="G21">
+        <v>1047.7439145531227</v>
+      </c>
+      <c r="H21">
+        <v>15.01110699893027</v>
+      </c>
+      <c r="I21">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K21">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>271</v>
+      </c>
+      <c r="B22">
+        <v>1276</v>
+      </c>
+      <c r="C22">
+        <v>1324</v>
+      </c>
+      <c r="D22">
+        <v>1299.778442658594</v>
+      </c>
+      <c r="E22">
+        <v>13.856406460551019</v>
+      </c>
+      <c r="F22">
+        <v>252.5</v>
+      </c>
+      <c r="G22">
+        <v>1026.778442658594</v>
+      </c>
+      <c r="H22">
+        <v>13.856406460551019</v>
+      </c>
+      <c r="I22">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K22">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>272</v>
+      </c>
+      <c r="B23">
+        <v>1264</v>
+      </c>
+      <c r="C23">
+        <v>1314</v>
+      </c>
+      <c r="D23">
+        <v>1288.7575412000506</v>
+      </c>
+      <c r="E23">
+        <v>14.433756729740645</v>
+      </c>
+      <c r="F23">
+        <v>253.5</v>
+      </c>
+      <c r="G23">
+        <v>1014.7575412000506</v>
+      </c>
+      <c r="H23">
+        <v>14.433756729740645</v>
+      </c>
+      <c r="I23">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>273</v>
+      </c>
+      <c r="B24">
+        <v>1241</v>
+      </c>
+      <c r="C24">
+        <v>1304</v>
+      </c>
+      <c r="D24">
+        <v>1272.1100581317639</v>
+      </c>
+      <c r="E24">
+        <v>18.186533479473212</v>
+      </c>
+      <c r="F24">
+        <v>254.5</v>
+      </c>
+      <c r="G24">
+        <v>997.11005813176394</v>
+      </c>
+      <c r="H24">
+        <v>18.186533479473212</v>
+      </c>
+      <c r="I24">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K24">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>274</v>
+      </c>
+      <c r="B25">
+        <v>1236</v>
+      </c>
+      <c r="C25">
+        <v>1289</v>
+      </c>
+      <c r="D25">
+        <v>1262.221850547676</v>
+      </c>
+      <c r="E25">
+        <v>15.299782133525083</v>
+      </c>
+      <c r="F25">
+        <v>255.5</v>
+      </c>
+      <c r="G25">
+        <v>986.22185054767601</v>
+      </c>
+      <c r="H25">
+        <v>15.299782133525083</v>
+      </c>
+      <c r="I25">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>275</v>
+      </c>
+      <c r="B26">
+        <v>1221</v>
+      </c>
+      <c r="C26">
+        <v>1268</v>
+      </c>
+      <c r="D26">
+        <v>1244.2781039622935</v>
+      </c>
+      <c r="E26">
+        <v>13.567731325956206</v>
+      </c>
+      <c r="F26">
+        <v>256.5</v>
+      </c>
+      <c r="G26">
+        <v>967.27810396229347</v>
+      </c>
+      <c r="H26">
+        <v>13.567731325956206</v>
+      </c>
+      <c r="I26">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K26">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>276</v>
+      </c>
+      <c r="B27">
+        <v>1206</v>
+      </c>
+      <c r="C27">
+        <v>1254</v>
+      </c>
+      <c r="D27">
+        <v>1229.7658313679071</v>
+      </c>
+      <c r="E27">
+        <v>13.856406460551019</v>
+      </c>
+      <c r="F27">
+        <v>257.5</v>
+      </c>
+      <c r="G27">
+        <v>951.76583136790714</v>
+      </c>
+      <c r="H27">
+        <v>13.856406460551019</v>
+      </c>
+      <c r="I27">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K27">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>277</v>
+      </c>
+      <c r="B28">
+        <v>1196</v>
+      </c>
+      <c r="C28">
+        <v>1234</v>
+      </c>
+      <c r="D28">
+        <v>1214.8514312458128</v>
+      </c>
+      <c r="E28">
+        <v>10.96965511460289</v>
+      </c>
+      <c r="F28">
+        <v>258.5</v>
+      </c>
+      <c r="G28">
+        <v>935.85143124581282</v>
+      </c>
+      <c r="H28">
+        <v>10.96965511460289</v>
+      </c>
+      <c r="I28">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K28">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>278</v>
+      </c>
+      <c r="B29">
+        <v>1180</v>
+      </c>
+      <c r="C29">
+        <v>1223</v>
+      </c>
+      <c r="D29">
+        <v>1201.307620886507</v>
+      </c>
+      <c r="E29">
+        <v>12.413030787576954</v>
+      </c>
+      <c r="F29">
+        <v>259.5</v>
+      </c>
+      <c r="G29">
+        <v>921.30762088650704</v>
+      </c>
+      <c r="H29">
+        <v>12.413030787576954</v>
+      </c>
+      <c r="I29">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K29">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>279</v>
+      </c>
+      <c r="B30">
+        <v>1176</v>
+      </c>
+      <c r="C30">
+        <v>1213</v>
+      </c>
+      <c r="D30">
+        <v>1194.3567306295049</v>
+      </c>
+      <c r="E30">
+        <v>10.680979980008077</v>
+      </c>
+      <c r="F30">
+        <v>260.5</v>
+      </c>
+      <c r="G30">
+        <v>913.35673062950491</v>
+      </c>
+      <c r="H30">
+        <v>10.680979980008077</v>
+      </c>
+      <c r="I30">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K30">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>280</v>
+      </c>
+      <c r="B31">
+        <v>1164</v>
+      </c>
+      <c r="C31">
+        <v>1205</v>
+      </c>
+      <c r="D31">
+        <v>1184.3225911887353</v>
+      </c>
+      <c r="E31">
+        <v>11.835680518387329</v>
+      </c>
+      <c r="F31">
+        <v>261.5</v>
+      </c>
+      <c r="G31">
+        <v>902.32259118873526</v>
+      </c>
+      <c r="H31">
+        <v>11.835680518387329</v>
+      </c>
+      <c r="I31">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>281</v>
+      </c>
+      <c r="B32">
+        <v>1153</v>
+      </c>
+      <c r="C32">
+        <v>1189</v>
+      </c>
+      <c r="D32">
+        <v>1170.8616485306879</v>
+      </c>
+      <c r="E32">
+        <v>10.392304845413264</v>
+      </c>
+      <c r="F32">
+        <v>262.5</v>
+      </c>
+      <c r="G32">
+        <v>887.86164853068794</v>
+      </c>
+      <c r="H32">
+        <v>10.392304845413264</v>
+      </c>
+      <c r="I32">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K32">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>282</v>
+      </c>
+      <c r="B33">
+        <v>1149</v>
+      </c>
+      <c r="C33">
+        <v>1182</v>
+      </c>
+      <c r="D33">
+        <v>1165.3831987805556</v>
+      </c>
+      <c r="E33">
+        <v>9.5262794416288248</v>
+      </c>
+      <c r="F33">
+        <v>263.5</v>
+      </c>
+      <c r="G33">
+        <v>881.38319878055563</v>
+      </c>
+      <c r="H33">
+        <v>9.5262794416288248</v>
+      </c>
+      <c r="I33">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K33">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>283</v>
+      </c>
+      <c r="B34">
+        <v>1136</v>
+      </c>
+      <c r="C34">
+        <v>1169</v>
+      </c>
+      <c r="D34">
+        <v>1152.3818811487797</v>
+      </c>
+      <c r="E34">
+        <v>9.5262794416288248</v>
+      </c>
+      <c r="F34">
+        <v>264.5</v>
+      </c>
+      <c r="G34">
+        <v>867.38188114877971</v>
+      </c>
+      <c r="H34">
+        <v>9.5262794416288248</v>
+      </c>
+      <c r="I34">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>284</v>
+      </c>
+      <c r="B35">
+        <v>1122</v>
+      </c>
+      <c r="C35">
+        <v>1163</v>
+      </c>
+      <c r="D35">
+        <v>1142.3160683453596</v>
+      </c>
+      <c r="E35">
+        <v>11.835680518387329</v>
+      </c>
+      <c r="F35">
+        <v>265.5</v>
+      </c>
+      <c r="G35">
+        <v>856.31606834535955</v>
+      </c>
+      <c r="H35">
+        <v>11.835680518387329</v>
+      </c>
+      <c r="I35">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>286</v>
+      </c>
+      <c r="B36">
+        <v>1110</v>
+      </c>
+      <c r="C36">
+        <v>1138</v>
+      </c>
+      <c r="D36">
+        <v>1123.9128080060302</v>
+      </c>
+      <c r="E36">
+        <v>8.0829037686547611</v>
+      </c>
+      <c r="F36">
+        <v>267.5</v>
+      </c>
+      <c r="G36">
+        <v>835.91280800603022</v>
+      </c>
+      <c r="H36">
+        <v>8.0829037686547611</v>
+      </c>
+      <c r="I36">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K36">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>288</v>
+      </c>
+      <c r="B37">
+        <v>1094</v>
+      </c>
+      <c r="C37">
+        <v>1121</v>
+      </c>
+      <c r="D37">
+        <v>1107.4177170336404</v>
+      </c>
+      <c r="E37">
+        <v>7.794228634059948</v>
+      </c>
+      <c r="F37">
+        <v>269.5</v>
+      </c>
+      <c r="G37">
+        <v>817.41771703364043</v>
+      </c>
+      <c r="H37">
+        <v>7.794228634059948</v>
+      </c>
+      <c r="I37">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K37">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>290</v>
+      </c>
+      <c r="B38">
+        <v>1076</v>
+      </c>
+      <c r="C38">
+        <v>1107</v>
+      </c>
+      <c r="D38">
+        <v>1091.3899394808439</v>
+      </c>
+      <c r="E38">
+        <v>8.9489291724392004</v>
+      </c>
+      <c r="F38">
+        <v>271.5</v>
+      </c>
+      <c r="G38">
+        <v>799.38993948084385</v>
+      </c>
+      <c r="H38">
+        <v>8.9489291724392004</v>
+      </c>
+      <c r="I38">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K38">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>292</v>
+      </c>
+      <c r="B39">
+        <v>1064</v>
+      </c>
+      <c r="C39">
+        <v>1092</v>
+      </c>
+      <c r="D39">
+        <v>1077.9090870755288</v>
+      </c>
+      <c r="E39">
+        <v>8.0829037686547611</v>
+      </c>
+      <c r="F39">
+        <v>273.5</v>
+      </c>
+      <c r="G39">
+        <v>783.90908707552876</v>
+      </c>
+      <c r="H39">
+        <v>8.0829037686547611</v>
+      </c>
+      <c r="I39">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K39">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>294</v>
+      </c>
+      <c r="B40">
+        <v>1048</v>
+      </c>
+      <c r="C40">
+        <v>1079</v>
+      </c>
+      <c r="D40">
+        <v>1063.3870414858363</v>
+      </c>
+      <c r="E40">
+        <v>8.9489291724392004</v>
+      </c>
+      <c r="F40">
+        <v>275.5</v>
+      </c>
+      <c r="G40">
+        <v>767.38704148583633</v>
+      </c>
+      <c r="H40">
+        <v>8.9489291724392004</v>
+      </c>
+      <c r="I40">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K40">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>296</v>
+      </c>
+      <c r="B41">
+        <v>1041</v>
+      </c>
+      <c r="C41">
+        <v>1064</v>
+      </c>
+      <c r="D41">
+        <v>1052.4371715214168</v>
+      </c>
+      <c r="E41">
+        <v>6.6395280956806966</v>
+      </c>
+      <c r="F41">
+        <v>277.5</v>
+      </c>
+      <c r="G41">
+        <v>754.43717152141676</v>
+      </c>
+      <c r="H41">
+        <v>6.6395280956806966</v>
+      </c>
+      <c r="I41">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>299</v>
+      </c>
+      <c r="B42">
+        <v>1015</v>
+      </c>
+      <c r="C42">
+        <v>1047</v>
+      </c>
+      <c r="D42">
+        <v>1030.875841214644</v>
+      </c>
+      <c r="E42">
+        <v>9.2376043070340135</v>
+      </c>
+      <c r="F42">
+        <v>280.5</v>
+      </c>
+      <c r="G42">
+        <v>729.87584121464397</v>
+      </c>
+      <c r="H42">
+        <v>9.2376043070340135</v>
+      </c>
+      <c r="I42">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K42">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>300</v>
+      </c>
+      <c r="B43">
+        <v>1011</v>
+      </c>
+      <c r="C43">
+        <v>1044</v>
+      </c>
+      <c r="D43">
+        <v>1027.3675097062394</v>
+      </c>
+      <c r="E43">
+        <v>9.5262794416288248</v>
+      </c>
+      <c r="F43">
+        <v>281.5</v>
+      </c>
+      <c r="G43">
+        <v>725.36750970623939</v>
+      </c>
+      <c r="H43">
+        <v>9.5262794416288248</v>
+      </c>
+      <c r="I43">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K43">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>301</v>
+      </c>
+      <c r="B44">
+        <v>1005</v>
+      </c>
+      <c r="C44">
+        <v>1037</v>
+      </c>
+      <c r="D44">
+        <v>1020.8746250152367</v>
+      </c>
+      <c r="E44">
+        <v>9.2376043070340135</v>
+      </c>
+      <c r="F44">
+        <v>282.5</v>
+      </c>
+      <c r="G44">
+        <v>717.87462501523669</v>
+      </c>
+      <c r="H44">
+        <v>9.2376043070340135</v>
+      </c>
+      <c r="I44">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K44">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>302</v>
+      </c>
+      <c r="B45">
+        <v>1001</v>
+      </c>
+      <c r="C45">
+        <v>1020</v>
+      </c>
+      <c r="D45">
+        <v>1010.4553429023966</v>
+      </c>
+      <c r="E45">
+        <v>5.4848275573014451</v>
+      </c>
+      <c r="F45">
+        <v>283.5</v>
+      </c>
+      <c r="G45">
+        <v>706.45534290239664</v>
+      </c>
+      <c r="H45">
+        <v>5.4848275573014451</v>
+      </c>
+      <c r="I45">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>303</v>
+      </c>
+      <c r="B46">
+        <v>992</v>
+      </c>
+      <c r="C46">
+        <v>1015</v>
+      </c>
+      <c r="D46">
+        <v>1003.43410346669</v>
+      </c>
+      <c r="E46">
+        <v>6.6395280956806966</v>
+      </c>
+      <c r="F46">
+        <v>284.5</v>
+      </c>
+      <c r="G46">
+        <v>698.43410346668998</v>
+      </c>
+      <c r="H46">
+        <v>6.6395280956806966</v>
+      </c>
+      <c r="I46">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K46">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>304</v>
+      </c>
+      <c r="B47">
+        <v>992</v>
+      </c>
+      <c r="C47">
+        <v>1015</v>
+      </c>
+      <c r="D47">
+        <v>1003.43410346669</v>
+      </c>
+      <c r="E47">
+        <v>6.6395280956806966</v>
+      </c>
+      <c r="F47">
+        <v>285.5</v>
+      </c>
+      <c r="G47">
+        <v>697.43410346668998</v>
+      </c>
+      <c r="H47">
+        <v>6.6395280956806966</v>
+      </c>
+      <c r="I47">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K47">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>305</v>
+      </c>
+      <c r="B48">
+        <v>986</v>
+      </c>
+      <c r="C48">
+        <v>1006</v>
+      </c>
+      <c r="D48">
+        <v>995.94979793160257</v>
+      </c>
+      <c r="E48">
+        <v>5.7735026918962582</v>
+      </c>
+      <c r="F48">
+        <v>286.5</v>
+      </c>
+      <c r="G48">
+        <v>688.94979793160257</v>
+      </c>
+      <c r="H48">
+        <v>5.7735026918962582</v>
+      </c>
+      <c r="I48">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>306</v>
+      </c>
+      <c r="B49">
+        <v>985</v>
+      </c>
+      <c r="C49">
+        <v>1000</v>
+      </c>
+      <c r="D49">
+        <v>992.47166206396048</v>
+      </c>
+      <c r="E49">
+        <v>4.3301270189221936</v>
+      </c>
+      <c r="F49">
+        <v>287.5</v>
+      </c>
+      <c r="G49">
+        <v>684.47166206396048</v>
+      </c>
+      <c r="H49">
+        <v>4.3301270189221936</v>
+      </c>
+      <c r="I49">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K49">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>307</v>
+      </c>
+      <c r="B50">
+        <v>981</v>
+      </c>
+      <c r="C50">
+        <v>999</v>
+      </c>
+      <c r="D50">
+        <v>989.95909006382692</v>
+      </c>
+      <c r="E50">
+        <v>5.196152422706632</v>
+      </c>
+      <c r="F50">
+        <v>288.5</v>
+      </c>
+      <c r="G50">
+        <v>680.95909006382692</v>
+      </c>
+      <c r="H50">
+        <v>5.196152422706632</v>
+      </c>
+      <c r="I50">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K50">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>308</v>
+      </c>
+      <c r="B51">
+        <v>975</v>
+      </c>
+      <c r="C51">
+        <v>992</v>
+      </c>
+      <c r="D51">
+        <v>983.46326825153972</v>
+      </c>
+      <c r="E51">
+        <v>4.9074772881118189</v>
+      </c>
+      <c r="F51">
+        <v>289.5</v>
+      </c>
+      <c r="G51">
+        <v>673.46326825153972</v>
+      </c>
+      <c r="H51">
+        <v>4.9074772881118189</v>
+      </c>
+      <c r="I51">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K51">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>309</v>
+      </c>
+      <c r="B52">
+        <v>971</v>
+      </c>
+      <c r="C52">
+        <v>988</v>
+      </c>
+      <c r="D52">
+        <v>979.46311824386737</v>
+      </c>
+      <c r="E52">
+        <v>4.9074772881118189</v>
+      </c>
+      <c r="F52">
+        <v>290.5</v>
+      </c>
+      <c r="G52">
+        <v>668.46311824386737</v>
+      </c>
+      <c r="H52">
+        <v>4.9074772881118189</v>
+      </c>
+      <c r="I52">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K52">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>310</v>
+      </c>
+      <c r="B53">
+        <v>968</v>
+      </c>
+      <c r="C53">
+        <v>987</v>
+      </c>
+      <c r="D53">
+        <v>977.45383522701468</v>
+      </c>
+      <c r="E53">
+        <v>5.4848275573014451</v>
+      </c>
+      <c r="F53">
+        <v>291.5</v>
+      </c>
+      <c r="G53">
+        <v>665.45383522701468</v>
+      </c>
+      <c r="H53">
+        <v>5.4848275573014451</v>
+      </c>
+      <c r="I53">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K53">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>311</v>
+      </c>
+      <c r="B54">
+        <v>965</v>
+      </c>
+      <c r="C54">
+        <v>974</v>
+      </c>
+      <c r="D54">
+        <v>969.48955641615851</v>
+      </c>
+      <c r="E54">
+        <v>2.598076211353316</v>
+      </c>
+      <c r="F54">
+        <v>292.5</v>
+      </c>
+      <c r="G54">
+        <v>656.48955641615851</v>
+      </c>
+      <c r="H54">
+        <v>2.598076211353316</v>
+      </c>
+      <c r="I54">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K54">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>312</v>
+      </c>
+      <c r="B55">
+        <v>960</v>
+      </c>
+      <c r="C55">
+        <v>976</v>
+      </c>
+      <c r="D55">
+        <v>967.96694158426715</v>
+      </c>
+      <c r="E55">
+        <v>4.6188021535170067</v>
+      </c>
+      <c r="F55">
+        <v>293.5</v>
+      </c>
+      <c r="G55">
+        <v>653.96694158426715</v>
+      </c>
+      <c r="H55">
+        <v>4.6188021535170067</v>
+      </c>
+      <c r="I55">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K55">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>313</v>
+      </c>
+      <c r="B56">
+        <v>957</v>
+      </c>
+      <c r="C56">
+        <v>969</v>
+      </c>
+      <c r="D56">
+        <v>962.98130822981193</v>
+      </c>
+      <c r="E56">
+        <v>3.4641016151377548</v>
+      </c>
+      <c r="F56">
+        <v>294.5</v>
+      </c>
+      <c r="G56">
+        <v>647.98130822981193</v>
+      </c>
+      <c r="H56">
+        <v>3.4641016151377548</v>
+      </c>
+      <c r="I56">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K56">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>314</v>
+      </c>
+      <c r="B57">
+        <v>955</v>
+      </c>
+      <c r="C57">
+        <v>967</v>
+      </c>
+      <c r="D57">
+        <v>960.98126932838807</v>
+      </c>
+      <c r="E57">
+        <v>3.4641016151377548</v>
+      </c>
+      <c r="F57">
+        <v>295.5</v>
+      </c>
+      <c r="G57">
+        <v>644.98126932838807</v>
+      </c>
+      <c r="H57">
+        <v>3.4641016151377548</v>
+      </c>
+      <c r="I57">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>316</v>
+      </c>
+      <c r="B58">
+        <v>945</v>
+      </c>
+      <c r="C58">
+        <v>961</v>
+      </c>
+      <c r="D58">
+        <v>952.9664212342426</v>
+      </c>
+      <c r="E58">
+        <v>4.6188021535170067</v>
+      </c>
+      <c r="F58">
+        <v>297.5</v>
+      </c>
+      <c r="G58">
+        <v>634.9664212342426</v>
+      </c>
+      <c r="H58">
+        <v>4.6188021535170067</v>
+      </c>
+      <c r="I58">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K58">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>318</v>
+      </c>
+      <c r="B59">
+        <v>940</v>
+      </c>
+      <c r="C59">
+        <v>953</v>
+      </c>
+      <c r="D59">
+        <v>946.47768066658602</v>
+      </c>
+      <c r="E59">
+        <v>3.7527767497325675</v>
+      </c>
+      <c r="F59">
+        <v>299.5</v>
+      </c>
+      <c r="G59">
+        <v>626.47768066658602</v>
+      </c>
+      <c r="H59">
+        <v>3.7527767497325675</v>
+      </c>
+      <c r="I59">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K59">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>320</v>
+      </c>
+      <c r="B60">
+        <v>929</v>
+      </c>
+      <c r="C60">
+        <v>945</v>
+      </c>
+      <c r="D60">
+        <v>936.96584783011167</v>
+      </c>
+      <c r="E60">
+        <v>4.6188021535170067</v>
+      </c>
+      <c r="F60">
+        <v>301.5</v>
+      </c>
+      <c r="G60">
+        <v>614.96584783011167</v>
+      </c>
+      <c r="H60">
+        <v>4.6188021535170067</v>
+      </c>
+      <c r="I60">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K60">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>325</v>
+      </c>
+      <c r="B61">
+        <v>916</v>
+      </c>
+      <c r="C61">
+        <v>930</v>
+      </c>
+      <c r="D61">
+        <v>922.97345573965447</v>
+      </c>
+      <c r="E61">
+        <v>4.0414518843273806</v>
+      </c>
+      <c r="F61">
+        <v>306.5</v>
+      </c>
+      <c r="G61">
+        <v>595.97345573965447</v>
+      </c>
+      <c r="H61">
+        <v>4.0414518843273806</v>
+      </c>
+      <c r="I61">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K61">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>330</v>
+      </c>
+      <c r="B62">
+        <v>906</v>
+      </c>
+      <c r="C62">
+        <v>915</v>
+      </c>
+      <c r="D62">
+        <v>910.48887966849986</v>
+      </c>
+      <c r="E62">
+        <v>2.598076211353316</v>
+      </c>
+      <c r="F62">
+        <v>311.5</v>
+      </c>
+      <c r="G62">
+        <v>578.48887966849986</v>
+      </c>
+      <c r="H62">
+        <v>2.598076211353316</v>
+      </c>
+      <c r="I62">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K62">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>335</v>
+      </c>
+      <c r="B63">
+        <v>886</v>
+      </c>
+      <c r="D63">
+        <v>886</v>
+      </c>
+      <c r="E63">
+        <v>255.76616925100421</v>
+      </c>
+      <c r="F63">
+        <v>316.5</v>
+      </c>
+      <c r="G63">
+        <v>549</v>
+      </c>
+      <c r="H63">
+        <v>255.76616925100421</v>
+      </c>
+      <c r="I63">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K63">
+        <v>-886</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>340</v>
+      </c>
+      <c r="B64">
+        <v>871</v>
+      </c>
+      <c r="D64">
+        <v>871</v>
+      </c>
+      <c r="E64">
+        <v>251.43604223208203</v>
+      </c>
+      <c r="F64">
+        <v>321.5</v>
+      </c>
+      <c r="G64">
+        <v>529</v>
+      </c>
+      <c r="H64">
+        <v>251.43604223208203</v>
+      </c>
+      <c r="I64">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K64">
+        <v>-871</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>345</v>
+      </c>
+      <c r="B65">
+        <v>870</v>
+      </c>
+      <c r="D65">
+        <v>870</v>
+      </c>
+      <c r="E65">
+        <v>251.14736709748723</v>
+      </c>
+      <c r="F65">
+        <v>326.5</v>
+      </c>
+      <c r="G65">
+        <v>523</v>
+      </c>
+      <c r="H65">
+        <v>251.14736709748723</v>
+      </c>
+      <c r="I65">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K65">
+        <v>-870</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>350</v>
+      </c>
+      <c r="B66">
+        <v>864</v>
+      </c>
+      <c r="D66">
+        <v>864</v>
+      </c>
+      <c r="E66">
+        <v>249.41531628991834</v>
+      </c>
+      <c r="F66">
+        <v>331.5</v>
+      </c>
+      <c r="G66">
+        <v>512</v>
+      </c>
+      <c r="H66">
+        <v>249.41531628991834</v>
+      </c>
+      <c r="I66">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K66">
+        <v>-864</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>355</v>
+      </c>
+      <c r="B67">
+        <v>856</v>
+      </c>
+      <c r="D67">
+        <v>856</v>
+      </c>
+      <c r="E67">
+        <v>247.10591521315985</v>
+      </c>
+      <c r="F67">
+        <v>336.5</v>
+      </c>
+      <c r="G67">
+        <v>499</v>
+      </c>
+      <c r="H67">
+        <v>247.10591521315985</v>
+      </c>
+      <c r="I67">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K67">
+        <v>-856</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>360</v>
+      </c>
+      <c r="B68">
+        <v>851</v>
+      </c>
+      <c r="D68">
+        <v>851</v>
+      </c>
+      <c r="E68">
+        <v>245.66253954018578</v>
+      </c>
+      <c r="F68">
+        <v>341.5</v>
+      </c>
+      <c r="G68">
+        <v>489</v>
+      </c>
+      <c r="H68">
+        <v>245.66253954018578</v>
+      </c>
+      <c r="I68">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K68">
+        <v>-851</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>365</v>
+      </c>
+      <c r="B69">
+        <v>846</v>
+      </c>
+      <c r="D69">
+        <v>846</v>
+      </c>
+      <c r="E69">
+        <v>244.21916386721171</v>
+      </c>
+      <c r="F69">
+        <v>346.5</v>
+      </c>
+      <c r="G69">
+        <v>479</v>
+      </c>
+      <c r="H69">
+        <v>244.21916386721171</v>
+      </c>
+      <c r="I69">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K69">
+        <v>-846</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>370</v>
+      </c>
+      <c r="B70">
+        <v>840</v>
+      </c>
+      <c r="D70">
+        <v>840</v>
+      </c>
+      <c r="E70">
+        <v>242.48711305964284</v>
+      </c>
+      <c r="F70">
+        <v>351.5</v>
+      </c>
+      <c r="G70">
+        <v>468</v>
+      </c>
+      <c r="H70">
+        <v>242.48711305964284</v>
+      </c>
+      <c r="I70">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K70">
+        <v>-840</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>375</v>
+      </c>
+      <c r="B71">
+        <v>835</v>
+      </c>
+      <c r="D71">
+        <v>835</v>
+      </c>
+      <c r="E71">
+        <v>241.04373738666877</v>
+      </c>
+      <c r="F71">
+        <v>356.5</v>
+      </c>
+      <c r="G71">
+        <v>458</v>
+      </c>
+      <c r="H71">
+        <v>241.04373738666877</v>
+      </c>
+      <c r="I71">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K71">
+        <v>-835</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>380</v>
+      </c>
+      <c r="B72">
+        <v>833</v>
+      </c>
+      <c r="D72">
+        <v>833</v>
+      </c>
+      <c r="E72">
+        <v>240.46638711747914</v>
+      </c>
+      <c r="F72">
+        <v>361.5</v>
+      </c>
+      <c r="G72">
+        <v>451</v>
+      </c>
+      <c r="H72">
+        <v>240.46638711747914</v>
+      </c>
+      <c r="I72">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K72">
+        <v>-833</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>385</v>
+      </c>
+      <c r="B73">
+        <v>832</v>
+      </c>
+      <c r="D73">
+        <v>832</v>
+      </c>
+      <c r="E73">
+        <v>240.17771198288432</v>
+      </c>
+      <c r="F73">
+        <v>366.5</v>
+      </c>
+      <c r="G73">
+        <v>445</v>
+      </c>
+      <c r="H73">
+        <v>240.17771198288432</v>
+      </c>
+      <c r="I73">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K73">
+        <v>-832</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>390</v>
+      </c>
+      <c r="B74">
+        <v>828</v>
+      </c>
+      <c r="D74">
+        <v>828</v>
+      </c>
+      <c r="E74">
+        <v>239.02301144450507</v>
+      </c>
+      <c r="F74">
+        <v>371.5</v>
+      </c>
+      <c r="G74">
+        <v>436</v>
+      </c>
+      <c r="H74">
+        <v>239.02301144450507</v>
+      </c>
+      <c r="I74">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K74">
+        <v>-828</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>395</v>
+      </c>
+      <c r="B75">
+        <v>825</v>
+      </c>
+      <c r="D75">
+        <v>825</v>
+      </c>
+      <c r="E75">
+        <v>238.15698604072065</v>
+      </c>
+      <c r="F75">
+        <v>376.5</v>
+      </c>
+      <c r="G75">
+        <v>428</v>
+      </c>
+      <c r="H75">
+        <v>238.15698604072065</v>
+      </c>
+      <c r="I75">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K75">
+        <v>-825</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>400</v>
+      </c>
+      <c r="B76">
+        <v>822</v>
+      </c>
+      <c r="D76">
+        <v>822</v>
+      </c>
+      <c r="E76">
+        <v>237.29096063693621</v>
+      </c>
+      <c r="F76">
+        <v>381.5</v>
+      </c>
+      <c r="G76">
+        <v>420</v>
+      </c>
+      <c r="H76">
+        <v>237.29096063693621</v>
+      </c>
+      <c r="I76">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K76">
+        <v>-822</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>405</v>
+      </c>
+      <c r="B77">
+        <v>820</v>
+      </c>
+      <c r="D77">
+        <v>820</v>
+      </c>
+      <c r="E77">
+        <v>236.71361036774658</v>
+      </c>
+      <c r="F77">
+        <v>386.5</v>
+      </c>
+      <c r="G77">
+        <v>413</v>
+      </c>
+      <c r="H77">
+        <v>236.71361036774658</v>
+      </c>
+      <c r="I77">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K77">
+        <v>-820</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>410</v>
+      </c>
+      <c r="B78">
+        <v>816</v>
+      </c>
+      <c r="D78">
+        <v>816</v>
+      </c>
+      <c r="E78">
+        <v>235.55890982936734</v>
+      </c>
+      <c r="F78">
+        <v>391.5</v>
+      </c>
+      <c r="G78">
+        <v>404</v>
+      </c>
+      <c r="H78">
+        <v>235.55890982936734</v>
+      </c>
+      <c r="I78">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K78">
+        <v>-816</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>415</v>
+      </c>
+      <c r="B79">
+        <v>814</v>
+      </c>
+      <c r="D79">
+        <v>814</v>
+      </c>
+      <c r="E79">
+        <v>234.98155956017769</v>
+      </c>
+      <c r="F79">
+        <v>396.5</v>
+      </c>
+      <c r="G79">
+        <v>397</v>
+      </c>
+      <c r="H79">
+        <v>234.98155956017769</v>
+      </c>
+      <c r="I79">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K79">
+        <v>-814</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>420</v>
+      </c>
+      <c r="B80">
+        <v>822</v>
+      </c>
+      <c r="D80">
+        <v>822</v>
+      </c>
+      <c r="E80">
+        <v>237.29096063693621</v>
+      </c>
+      <c r="F80">
+        <v>401.5</v>
+      </c>
+      <c r="G80">
+        <v>400</v>
+      </c>
+      <c r="H80">
+        <v>237.29096063693621</v>
+      </c>
+      <c r="I80">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K80">
+        <v>-822</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>425</v>
+      </c>
+      <c r="B81">
+        <v>825</v>
+      </c>
+      <c r="D81">
+        <v>825</v>
+      </c>
+      <c r="E81">
+        <v>238.15698604072065</v>
+      </c>
+      <c r="F81">
+        <v>406.5</v>
+      </c>
+      <c r="G81">
+        <v>398</v>
+      </c>
+      <c r="H81">
+        <v>238.15698604072065</v>
+      </c>
+      <c r="I81">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K81">
+        <v>-825</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>430</v>
+      </c>
+      <c r="B82">
+        <v>827</v>
+      </c>
+      <c r="D82">
+        <v>827</v>
+      </c>
+      <c r="E82">
+        <v>238.73433630991028</v>
+      </c>
+      <c r="F82">
+        <v>411.5</v>
+      </c>
+      <c r="G82">
+        <v>395</v>
+      </c>
+      <c r="H82">
+        <v>238.73433630991028</v>
+      </c>
+      <c r="I82">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K82">
+        <v>-827</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>435</v>
+      </c>
+      <c r="B83">
+        <v>827</v>
+      </c>
+      <c r="D83">
+        <v>827</v>
+      </c>
+      <c r="E83">
+        <v>238.73433630991028</v>
+      </c>
+      <c r="F83">
+        <v>416.5</v>
+      </c>
+      <c r="G83">
+        <v>390</v>
+      </c>
+      <c r="H83">
+        <v>238.73433630991028</v>
+      </c>
+      <c r="I83">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K83">
+        <v>-827</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>440</v>
+      </c>
+      <c r="B84">
+        <v>829</v>
+      </c>
+      <c r="D84">
+        <v>829</v>
+      </c>
+      <c r="E84">
+        <v>239.3116865790999</v>
+      </c>
+      <c r="F84">
+        <v>421.5</v>
+      </c>
+      <c r="G84">
+        <v>387</v>
+      </c>
+      <c r="H84">
+        <v>239.3116865790999</v>
+      </c>
+      <c r="I84">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K84">
+        <v>-829</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>445</v>
+      </c>
+      <c r="B85">
+        <v>830</v>
+      </c>
+      <c r="D85">
+        <v>830</v>
+      </c>
+      <c r="E85">
+        <v>239.6003617136947</v>
+      </c>
+      <c r="F85">
+        <v>426.5</v>
+      </c>
+      <c r="G85">
+        <v>383</v>
+      </c>
+      <c r="H85">
+        <v>239.6003617136947</v>
+      </c>
+      <c r="I85">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K85">
+        <v>-830</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>450</v>
+      </c>
+      <c r="B86">
+        <v>831</v>
+      </c>
+      <c r="D86">
+        <v>831</v>
+      </c>
+      <c r="E86">
+        <v>239.88903684828952</v>
+      </c>
+      <c r="F86">
+        <v>431.5</v>
+      </c>
+      <c r="G86">
+        <v>379</v>
+      </c>
+      <c r="H86">
+        <v>239.88903684828952</v>
+      </c>
+      <c r="I86">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K86">
+        <v>-831</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>460</v>
+      </c>
+      <c r="B87">
+        <v>832</v>
+      </c>
+      <c r="D87">
+        <v>832</v>
+      </c>
+      <c r="E87">
+        <v>240.17771198288432</v>
+      </c>
+      <c r="F87">
+        <v>441.5</v>
+      </c>
+      <c r="G87">
+        <v>370</v>
+      </c>
+      <c r="H87">
+        <v>240.17771198288432</v>
+      </c>
+      <c r="I87">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K87">
+        <v>-832</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>470</v>
+      </c>
+      <c r="B88">
+        <v>837</v>
+      </c>
+      <c r="D88">
+        <v>837</v>
+      </c>
+      <c r="E88">
+        <v>241.62108765585839</v>
+      </c>
+      <c r="F88">
+        <v>451.5</v>
+      </c>
+      <c r="G88">
+        <v>365</v>
+      </c>
+      <c r="H88">
+        <v>241.62108765585839</v>
+      </c>
+      <c r="I88">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K88">
+        <v>-837</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>480</v>
+      </c>
+      <c r="B89">
+        <v>840</v>
+      </c>
+      <c r="D89">
+        <v>840</v>
+      </c>
+      <c r="E89">
+        <v>242.48711305964284</v>
+      </c>
+      <c r="F89">
+        <v>461.5</v>
+      </c>
+      <c r="G89">
+        <v>358</v>
+      </c>
+      <c r="H89">
+        <v>242.48711305964284</v>
+      </c>
+      <c r="I89">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K89">
+        <v>-840</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>490</v>
+      </c>
+      <c r="B90">
+        <v>835</v>
+      </c>
+      <c r="D90">
+        <v>835</v>
+      </c>
+      <c r="E90">
+        <v>241.04373738666877</v>
+      </c>
+      <c r="F90">
+        <v>471.5</v>
+      </c>
+      <c r="G90">
+        <v>343</v>
+      </c>
+      <c r="H90">
+        <v>241.04373738666877</v>
+      </c>
+      <c r="I90">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K90">
+        <v>-835</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>500</v>
+      </c>
+      <c r="B91">
+        <v>850</v>
+      </c>
+      <c r="D91">
+        <v>850</v>
+      </c>
+      <c r="E91">
+        <v>245.37386440559095</v>
+      </c>
+      <c r="F91">
+        <v>481.5</v>
+      </c>
+      <c r="G91">
+        <v>348</v>
+      </c>
+      <c r="H91">
+        <v>245.37386440559095</v>
+      </c>
+      <c r="I91">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K91">
+        <v>-850</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>510</v>
+      </c>
+      <c r="B92">
+        <v>855</v>
+      </c>
+      <c r="D92">
+        <v>855</v>
+      </c>
+      <c r="E92">
+        <v>246.81724007856502</v>
+      </c>
+      <c r="F92">
+        <v>491.5</v>
+      </c>
+      <c r="G92">
+        <v>343</v>
+      </c>
+      <c r="H92">
+        <v>246.81724007856502</v>
+      </c>
+      <c r="I92">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K92">
+        <v>-855</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>520</v>
+      </c>
+      <c r="B93">
+        <v>860</v>
+      </c>
+      <c r="D93">
+        <v>860</v>
+      </c>
+      <c r="E93">
+        <v>248.26061575153909</v>
+      </c>
+      <c r="F93">
+        <v>501.5</v>
+      </c>
+      <c r="G93">
+        <v>338</v>
+      </c>
+      <c r="H93">
+        <v>248.26061575153909</v>
+      </c>
+      <c r="I93">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K93">
+        <v>-860</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>530</v>
+      </c>
+      <c r="B94">
+        <v>865</v>
+      </c>
+      <c r="D94">
+        <v>865</v>
+      </c>
+      <c r="E94">
+        <v>249.70399142451316</v>
+      </c>
+      <c r="F94">
+        <v>511.5</v>
+      </c>
+      <c r="G94">
+        <v>333</v>
+      </c>
+      <c r="H94">
+        <v>249.70399142451316</v>
+      </c>
+      <c r="I94">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K94">
+        <v>-865</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>540</v>
+      </c>
+      <c r="B95">
+        <v>870</v>
+      </c>
+      <c r="D95">
+        <v>870</v>
+      </c>
+      <c r="E95">
+        <v>251.14736709748723</v>
+      </c>
+      <c r="F95">
+        <v>521.5</v>
+      </c>
+      <c r="G95">
+        <v>328</v>
+      </c>
+      <c r="H95">
+        <v>251.14736709748723</v>
+      </c>
+      <c r="I95">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K95">
+        <v>-870</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>550</v>
+      </c>
+      <c r="B96">
+        <v>875</v>
+      </c>
+      <c r="D96">
+        <v>875</v>
+      </c>
+      <c r="E96">
+        <v>252.59074277046128</v>
+      </c>
+      <c r="F96">
+        <v>531.5</v>
+      </c>
+      <c r="G96">
+        <v>323</v>
+      </c>
+      <c r="H96">
+        <v>252.59074277046128</v>
+      </c>
+      <c r="I96">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K96">
+        <v>-875</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>560</v>
+      </c>
+      <c r="B97">
+        <v>885</v>
+      </c>
+      <c r="D97">
+        <v>885</v>
+      </c>
+      <c r="E97">
+        <v>255.47749411640942</v>
+      </c>
+      <c r="F97">
+        <v>541.5</v>
+      </c>
+      <c r="G97">
+        <v>323</v>
+      </c>
+      <c r="H97">
+        <v>255.47749411640942</v>
+      </c>
+      <c r="I97">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K97">
+        <v>-885</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>570</v>
+      </c>
+      <c r="B98">
+        <v>890</v>
+      </c>
+      <c r="D98">
+        <v>890</v>
+      </c>
+      <c r="E98">
+        <v>256.92086978938346</v>
+      </c>
+      <c r="F98">
+        <v>551.5</v>
+      </c>
+      <c r="G98">
+        <v>318</v>
+      </c>
+      <c r="H98">
+        <v>256.92086978938346</v>
+      </c>
+      <c r="I98">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K98">
+        <v>-890</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>580</v>
+      </c>
+      <c r="B99">
+        <v>897</v>
+      </c>
+      <c r="D99">
+        <v>897</v>
+      </c>
+      <c r="E99">
+        <v>258.94159573154718</v>
+      </c>
+      <c r="F99">
+        <v>561.5</v>
+      </c>
+      <c r="G99">
+        <v>315</v>
+      </c>
+      <c r="H99">
+        <v>258.94159573154718</v>
+      </c>
+      <c r="I99">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K99">
+        <v>-897</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>590</v>
+      </c>
+      <c r="B100">
+        <v>905</v>
+      </c>
+      <c r="D100">
+        <v>905</v>
+      </c>
+      <c r="E100">
+        <v>261.25099680830567</v>
+      </c>
+      <c r="F100">
+        <v>571.5</v>
+      </c>
+      <c r="G100">
+        <v>313</v>
+      </c>
+      <c r="H100">
+        <v>261.25099680830567</v>
+      </c>
+      <c r="I100">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K100">
+        <v>-905</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>600</v>
+      </c>
+      <c r="B101">
+        <v>910</v>
+      </c>
+      <c r="D101">
+        <v>910</v>
+      </c>
+      <c r="E101">
+        <v>262.69437248127974</v>
+      </c>
+      <c r="F101">
+        <v>581.5</v>
+      </c>
+      <c r="G101">
+        <v>308</v>
+      </c>
+      <c r="H101">
+        <v>262.69437248127974</v>
+      </c>
+      <c r="I101">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K101">
+        <v>-910</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>620</v>
+      </c>
+      <c r="B102">
+        <v>925</v>
+      </c>
+      <c r="D102">
+        <v>925</v>
+      </c>
+      <c r="E102">
+        <v>267.02449950020196</v>
+      </c>
+      <c r="F102">
+        <v>601.5</v>
+      </c>
+      <c r="G102">
+        <v>303</v>
+      </c>
+      <c r="H102">
+        <v>267.02449950020196</v>
+      </c>
+      <c r="I102">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K102">
+        <v>-925</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>640</v>
+      </c>
+      <c r="B103">
+        <v>939</v>
+      </c>
+      <c r="D103">
+        <v>939</v>
+      </c>
+      <c r="E103">
+        <v>271.06595138452928</v>
+      </c>
+      <c r="F103">
+        <v>621.5</v>
+      </c>
+      <c r="G103">
+        <v>297</v>
+      </c>
+      <c r="H103">
+        <v>271.06595138452928</v>
+      </c>
+      <c r="I103">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K103">
+        <v>-939</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>660</v>
+      </c>
+      <c r="B104">
+        <v>958</v>
+      </c>
+      <c r="D104">
+        <v>958</v>
+      </c>
+      <c r="E104">
+        <v>276.55077894183074</v>
+      </c>
+      <c r="F104">
+        <v>641.5</v>
+      </c>
+      <c r="G104">
+        <v>296</v>
+      </c>
+      <c r="H104">
+        <v>276.55077894183074</v>
+      </c>
+      <c r="I104">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K104">
+        <v>-958</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>680</v>
+      </c>
+      <c r="B105">
+        <v>972</v>
+      </c>
+      <c r="D105">
+        <v>972</v>
+      </c>
+      <c r="E105">
+        <v>280.59223082615813</v>
+      </c>
+      <c r="F105">
+        <v>661.5</v>
+      </c>
+      <c r="G105">
+        <v>290</v>
+      </c>
+      <c r="H105">
+        <v>280.59223082615813</v>
+      </c>
+      <c r="I105">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K105">
+        <v>-972</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>700</v>
+      </c>
+      <c r="B106">
+        <v>990</v>
+      </c>
+      <c r="D106">
+        <v>990</v>
+      </c>
+      <c r="E106">
+        <v>285.78838324886476</v>
+      </c>
+      <c r="F106">
+        <v>681.5</v>
+      </c>
+      <c r="G106">
+        <v>288</v>
+      </c>
+      <c r="H106">
+        <v>285.78838324886476</v>
+      </c>
+      <c r="I106">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K106">
+        <v>-990</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>750</v>
+      </c>
+      <c r="B107">
+        <v>1030</v>
+      </c>
+      <c r="D107">
+        <v>1030</v>
+      </c>
+      <c r="E107">
+        <v>297.33538863265727</v>
+      </c>
+      <c r="F107">
+        <v>731.5</v>
+      </c>
+      <c r="G107">
+        <v>278</v>
+      </c>
+      <c r="H107">
+        <v>297.33538863265727</v>
+      </c>
+      <c r="I107">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K107">
+        <v>-1030</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>800</v>
+      </c>
+      <c r="B108">
+        <v>1073</v>
+      </c>
+      <c r="D108">
+        <v>1073</v>
+      </c>
+      <c r="E108">
+        <v>309.74841942023426</v>
+      </c>
+      <c r="F108">
+        <v>781.5</v>
+      </c>
+      <c r="G108">
+        <v>271</v>
+      </c>
+      <c r="H108">
+        <v>309.74841942023426</v>
+      </c>
+      <c r="I108">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K108">
+        <v>-1073</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>850</v>
+      </c>
+      <c r="B109">
+        <v>1118</v>
+      </c>
+      <c r="D109">
+        <v>1118</v>
+      </c>
+      <c r="E109">
+        <v>322.73880047700084</v>
+      </c>
+      <c r="F109">
+        <v>831.5</v>
+      </c>
+      <c r="G109">
+        <v>266</v>
+      </c>
+      <c r="H109">
+        <v>322.73880047700084</v>
+      </c>
+      <c r="I109">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K109">
+        <v>-1118</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>900</v>
+      </c>
+      <c r="B110">
+        <v>1164</v>
+      </c>
+      <c r="D110">
+        <v>1164</v>
+      </c>
+      <c r="E110">
+        <v>336.01785666836224</v>
+      </c>
+      <c r="F110">
+        <v>881.5</v>
+      </c>
+      <c r="G110">
+        <v>262</v>
+      </c>
+      <c r="H110">
+        <v>336.01785666836224</v>
+      </c>
+      <c r="I110">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K110">
+        <v>-1164</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>1000</v>
+      </c>
+      <c r="B111">
+        <v>1255</v>
+      </c>
+      <c r="D111">
+        <v>1255</v>
+      </c>
+      <c r="E111">
+        <v>362.28729391649017</v>
+      </c>
+      <c r="F111">
+        <v>981.5</v>
+      </c>
+      <c r="G111">
+        <v>253</v>
+      </c>
+      <c r="H111">
+        <v>362.28729391649017</v>
+      </c>
+      <c r="I111">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K111">
+        <v>-1255</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>1100</v>
+      </c>
+      <c r="B112">
+        <v>1349</v>
+      </c>
+      <c r="D112">
+        <v>1349</v>
+      </c>
+      <c r="E112">
+        <v>389.42275656840258</v>
+      </c>
+      <c r="F112">
+        <v>1081.5</v>
+      </c>
+      <c r="G112">
+        <v>247</v>
+      </c>
+      <c r="H112">
+        <v>389.42275656840258</v>
+      </c>
+      <c r="I112">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K112">
+        <v>-1349</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>1200</v>
+      </c>
+      <c r="B113">
+        <v>1445</v>
+      </c>
+      <c r="D113">
+        <v>1445</v>
+      </c>
+      <c r="E113">
+        <v>417.13556948950463</v>
+      </c>
+      <c r="F113">
+        <v>1181.5</v>
+      </c>
+      <c r="G113">
+        <v>243</v>
+      </c>
+      <c r="H113">
+        <v>417.13556948950463</v>
+      </c>
+      <c r="I113">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K113">
+        <v>-1445</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>1300</v>
+      </c>
+      <c r="B114">
+        <v>1542</v>
+      </c>
+      <c r="D114">
+        <v>1542</v>
+      </c>
+      <c r="E114">
+        <v>445.13705754520151</v>
+      </c>
+      <c r="F114">
+        <v>1281.5</v>
+      </c>
+      <c r="G114">
+        <v>240</v>
+      </c>
+      <c r="H114">
+        <v>445.13705754520151</v>
+      </c>
+      <c r="I114">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K114">
+        <v>-1542</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>1400</v>
+      </c>
+      <c r="B115">
+        <v>1638</v>
+      </c>
+      <c r="D115">
+        <v>1638</v>
+      </c>
+      <c r="E115">
+        <v>472.84987046630351</v>
+      </c>
+      <c r="F115">
+        <v>1381.5</v>
+      </c>
+      <c r="G115">
+        <v>236</v>
+      </c>
+      <c r="H115">
+        <v>472.84987046630351</v>
+      </c>
+      <c r="I115">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K115">
+        <v>-1638</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>1500</v>
+      </c>
+      <c r="B116">
+        <v>1736</v>
+      </c>
+      <c r="D116">
+        <v>1736</v>
+      </c>
+      <c r="E116">
+        <v>501.14003365659516</v>
+      </c>
+      <c r="F116">
+        <v>1481.5</v>
+      </c>
+      <c r="G116">
+        <v>234</v>
+      </c>
+      <c r="H116">
+        <v>501.14003365659516</v>
+      </c>
+      <c r="I116">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K116">
+        <v>-1736</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>1650</v>
+      </c>
+      <c r="B117">
+        <v>1882</v>
+      </c>
+      <c r="D117">
+        <v>1882</v>
+      </c>
+      <c r="E117">
+        <v>543.28660330743787</v>
+      </c>
+      <c r="F117">
+        <v>1631.5</v>
+      </c>
+      <c r="G117">
+        <v>230</v>
+      </c>
+      <c r="H117">
+        <v>543.28660330743787</v>
+      </c>
+      <c r="I117">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="K117">
+        <v>-1882</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D284FF1A-0AFF-4D5D-8003-93DAC2E72B22}">
   <dimension ref="A1:J130"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -24794,7 +28404,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>270</v>
       </c>
@@ -24826,7 +28436,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A47" si="0">A2+1</f>
         <v>271</v>
@@ -24859,7 +28469,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>272</v>
@@ -24892,7 +28502,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>273</v>
@@ -24925,7 +28535,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>274</v>
@@ -24958,7 +28568,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>275</v>
@@ -24991,7 +28601,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>276</v>
@@ -25024,7 +28634,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>277</v>
@@ -25057,7 +28667,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>278</v>
@@ -25090,7 +28700,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>279</v>
@@ -25123,7 +28733,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>280</v>
@@ -25156,7 +28766,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>281</v>
@@ -25189,7 +28799,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>282</v>
@@ -25222,7 +28832,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>283</v>
@@ -25255,7 +28865,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>284</v>
@@ -25288,7 +28898,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>285</v>
@@ -25321,7 +28931,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>286</v>
@@ -25354,7 +28964,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>287</v>
@@ -25387,7 +28997,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>288</v>
@@ -25420,7 +29030,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>289</v>
@@ -25453,7 +29063,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>290</v>
@@ -25486,7 +29096,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>291</v>
@@ -25519,7 +29129,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>292</v>
@@ -25552,7 +29162,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>293</v>
@@ -25585,7 +29195,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>294</v>
@@ -25618,7 +29228,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>295</v>
@@ -25651,7 +29261,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>296</v>
@@ -25684,7 +29294,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>297</v>
@@ -25717,7 +29327,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>298</v>
@@ -25750,7 +29360,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>299</v>
@@ -25783,7 +29393,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>300</v>
@@ -25816,7 +29426,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>301</v>
@@ -25849,7 +29459,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>302</v>
@@ -25882,7 +29492,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>303</v>
@@ -25915,7 +29525,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>304</v>
@@ -25948,7 +29558,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>305</v>
@@ -25981,7 +29591,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>306</v>
@@ -26014,7 +29624,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>307</v>
@@ -26047,7 +29657,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>308</v>
@@ -26080,7 +29690,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>309</v>
@@ -26113,7 +29723,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>310</v>
@@ -26146,7 +29756,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>311</v>
@@ -26179,7 +29789,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>312</v>
@@ -26212,7 +29822,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>313</v>
@@ -26245,7 +29855,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>314</v>
@@ -26278,7 +29888,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>315</v>
@@ -26311,7 +29921,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <f>A47+2</f>
         <v>317</v>
@@ -26344,7 +29954,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <f t="shared" ref="A49:A65" si="3">A48+2</f>
         <v>319</v>
@@ -26377,7 +29987,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <f t="shared" si="3"/>
         <v>321</v>
@@ -26410,7 +30020,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <f t="shared" si="3"/>
         <v>323</v>
@@ -26443,7 +30053,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <f t="shared" si="3"/>
         <v>325</v>
@@ -26476,7 +30086,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <f t="shared" si="3"/>
         <v>327</v>
@@ -26509,7 +30119,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <f t="shared" si="3"/>
         <v>329</v>
@@ -26542,7 +30152,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <f t="shared" si="3"/>
         <v>331</v>
@@ -26575,7 +30185,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <f t="shared" si="3"/>
         <v>333</v>
@@ -26608,7 +30218,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <f t="shared" si="3"/>
         <v>335</v>
@@ -26641,7 +30251,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <f t="shared" si="3"/>
         <v>337</v>
@@ -26674,7 +30284,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <f t="shared" si="3"/>
         <v>339</v>
@@ -26707,7 +30317,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <f t="shared" si="3"/>
         <v>341</v>
@@ -26740,7 +30350,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <f t="shared" si="3"/>
         <v>343</v>
@@ -26773,7 +30383,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <f t="shared" si="3"/>
         <v>345</v>
@@ -26806,7 +30416,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <f t="shared" si="3"/>
         <v>347</v>
@@ -26839,7 +30449,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <f t="shared" si="3"/>
         <v>349</v>
@@ -26872,7 +30482,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <f t="shared" si="3"/>
         <v>351</v>
@@ -26905,7 +30515,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <f>A65+3</f>
         <v>354</v>
@@ -26938,7 +30548,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <f t="shared" ref="A67:A73" si="4">A66+3</f>
         <v>357</v>
@@ -26971,7 +30581,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <f t="shared" si="4"/>
         <v>360</v>
@@ -27004,7 +30614,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <f t="shared" si="4"/>
         <v>363</v>
@@ -27037,7 +30647,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <f t="shared" si="4"/>
         <v>366</v>
@@ -27070,7 +30680,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <f t="shared" si="4"/>
         <v>369</v>
@@ -27103,7 +30713,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <f t="shared" si="4"/>
         <v>372</v>
@@ -27136,7 +30746,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <f t="shared" si="4"/>
         <v>375</v>
@@ -27169,7 +30779,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <f>A73+4</f>
         <v>379</v>
@@ -27202,7 +30812,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <f t="shared" ref="A75:A81" si="7">A74+4</f>
         <v>383</v>
@@ -27235,7 +30845,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <f t="shared" si="7"/>
         <v>387</v>
@@ -27268,7 +30878,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <f t="shared" si="7"/>
         <v>391</v>
@@ -27301,7 +30911,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <f t="shared" si="7"/>
         <v>395</v>
@@ -27334,7 +30944,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <f t="shared" si="7"/>
         <v>399</v>
@@ -27367,7 +30977,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <f t="shared" si="7"/>
         <v>403</v>
@@ -27400,7 +31010,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <f t="shared" si="7"/>
         <v>407</v>
@@ -27433,7 +31043,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <f>A81+5</f>
         <v>412</v>
@@ -27466,7 +31076,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <f t="shared" ref="A83:A89" si="8">A82+5</f>
         <v>417</v>
@@ -27499,7 +31109,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <f t="shared" si="8"/>
         <v>422</v>
@@ -27532,7 +31142,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <f t="shared" si="8"/>
         <v>427</v>
@@ -27565,7 +31175,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <f t="shared" si="8"/>
         <v>432</v>
@@ -27598,7 +31208,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <f t="shared" si="8"/>
         <v>437</v>
@@ -27631,7 +31241,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <f t="shared" si="8"/>
         <v>442</v>
@@ -27664,7 +31274,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <f t="shared" si="8"/>
         <v>447</v>
@@ -27697,7 +31307,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <f>A89+7</f>
         <v>454</v>
@@ -27730,7 +31340,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <f>A90+7</f>
         <v>461</v>
@@ -27763,7 +31373,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <f>A91+7</f>
         <v>468</v>
@@ -27796,7 +31406,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <f>A92+7</f>
         <v>475</v>
@@ -27829,7 +31439,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <f>A93+10</f>
         <v>485</v>
@@ -27862,7 +31472,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <f t="shared" ref="A95:A103" si="9">A94+10</f>
         <v>495</v>
@@ -27895,7 +31505,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <f t="shared" si="9"/>
         <v>505</v>
@@ -27928,7 +31538,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <f t="shared" si="9"/>
         <v>515</v>
@@ -27961,7 +31571,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <f t="shared" si="9"/>
         <v>525</v>
@@ -27994,7 +31604,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <f t="shared" si="9"/>
         <v>535</v>
@@ -28027,7 +31637,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <f t="shared" si="9"/>
         <v>545</v>
@@ -28060,7 +31670,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <f t="shared" si="9"/>
         <v>555</v>
@@ -28093,7 +31703,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <f t="shared" si="9"/>
         <v>565</v>
@@ -28126,7 +31736,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <f t="shared" si="9"/>
         <v>575</v>
@@ -28159,7 +31769,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <f>A103+20</f>
         <v>595</v>
@@ -28192,7 +31802,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <f t="shared" ref="A105:A113" si="10">A104+20</f>
         <v>615</v>
@@ -28225,7 +31835,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <f t="shared" si="10"/>
         <v>635</v>
@@ -28258,7 +31868,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <f t="shared" si="10"/>
         <v>655</v>
@@ -28291,7 +31901,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <f t="shared" si="10"/>
         <v>675</v>
@@ -28324,7 +31934,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <f t="shared" si="10"/>
         <v>695</v>
@@ -28357,7 +31967,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <f t="shared" si="10"/>
         <v>715</v>
@@ -28390,7 +32000,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <f t="shared" si="10"/>
         <v>735</v>
@@ -28423,7 +32033,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <f t="shared" si="10"/>
         <v>755</v>
@@ -28456,7 +32066,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <f t="shared" si="10"/>
         <v>775</v>
@@ -28489,7 +32099,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <f t="shared" ref="A114:A119" si="11">A113+50</f>
         <v>825</v>
@@ -28522,7 +32132,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <f t="shared" si="11"/>
         <v>875</v>
@@ -28555,7 +32165,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <f t="shared" si="11"/>
         <v>925</v>
@@ -28588,7 +32198,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <f t="shared" si="11"/>
         <v>975</v>
@@ -28621,7 +32231,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <f t="shared" si="11"/>
         <v>1025</v>
@@ -28654,7 +32264,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <f t="shared" si="11"/>
         <v>1075</v>
@@ -28687,7 +32297,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <f t="shared" ref="A120:A125" si="12">A119+100</f>
         <v>1175</v>
@@ -28720,7 +32330,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <f t="shared" si="12"/>
         <v>1275</v>
@@ -28753,7 +32363,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <f t="shared" si="12"/>
         <v>1375</v>
@@ -28786,7 +32396,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <f t="shared" si="12"/>
         <v>1475</v>
@@ -28819,7 +32429,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <f t="shared" si="12"/>
         <v>1575</v>
@@ -28852,7 +32462,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <f t="shared" si="12"/>
         <v>1675</v>
@@ -28885,19 +32495,19 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H126" s="3"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H127" s="3"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H128" s="3"/>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H129" s="3"/>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H130" s="3"/>
     </row>
   </sheetData>
@@ -28908,11 +32518,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="21343963-c43f-42a4-b0bc-b203e64410f4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -29098,26 +32709,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="21343963-c43f-42a4-b0bc-b203e64410f4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2150DC1C-3B4F-45D5-BBC6-27ED552170CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85EBBE4C-4513-4684-8667-BB58B10945F3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="21343963-c43f-42a4-b0bc-b203e64410f4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -29141,9 +32743,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85EBBE4C-4513-4684-8667-BB58B10945F3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2150DC1C-3B4F-45D5-BBC6-27ED552170CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="21343963-c43f-42a4-b0bc-b203e64410f4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Laboratorio/esperienza2/esperienza2.xlsx
+++ b/Laboratorio/esperienza2/esperienza2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michele/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B0C243-7D7A-5348-8399-B98354511DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D9BD58-CF2D-1D45-98A9-42808ECA812B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8840" yWindow="3340" windowWidth="25360" windowHeight="15000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,6 +113,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -157,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -177,6 +181,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -483,7 +494,9 @@
     <col min="1" max="1" width="12.5" style="5" customWidth="1"/>
     <col min="2" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="6" customWidth="1"/>
-    <col min="5" max="10" width="12.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="10" customWidth="1"/>
+    <col min="7" max="10" width="12.5" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -502,7 +515,7 @@
       <c r="E1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -529,7 +542,7 @@
       <c r="E2" s="1">
         <v>1975</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="11">
         <f>IF(C2=0, Parametri!$D$8, ABS(B2-C2)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -562,7 +575,7 @@
       <c r="E3" s="1">
         <v>1975</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="11">
         <f>IF(C3=0, Parametri!$D$8, ABS(B3-C3)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -595,7 +608,7 @@
       <c r="E4" s="1">
         <v>1912</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="11">
         <f>IF(C4=0, Parametri!$D$8, ABS(B4-C4)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -628,7 +641,7 @@
       <c r="E5" s="1">
         <v>1893</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="11">
         <f>IF(C5=0, Parametri!$D$8, ABS(B5-C5)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -661,7 +674,7 @@
       <c r="E6" s="1">
         <v>1817</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="11">
         <f>IF(C6=0, Parametri!$D$8, ABS(B6-C6)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -694,7 +707,7 @@
       <c r="E7" s="1">
         <v>1783</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="11">
         <f>IF(C7=0, Parametri!$D$8, ABS(B7-C7)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -727,7 +740,7 @@
       <c r="E8" s="1">
         <v>1723.5</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="11">
         <f>IF(C8=0, Parametri!$D$8, ABS(B8-C8)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -760,7 +773,7 @@
       <c r="E9" s="1">
         <v>1676</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="11">
         <f>IF(C9=0, Parametri!$D$8, ABS(B9-C9)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -793,7 +806,7 @@
       <c r="E10" s="1">
         <v>1660</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="11">
         <f>IF(C10=0, Parametri!$D$8, ABS(B10-C10)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -826,7 +839,7 @@
       <c r="E11" s="1">
         <v>1615.5</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="11">
         <f>IF(C11=0, Parametri!$D$8, ABS(B11-C11)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -859,7 +872,7 @@
       <c r="E12" s="1">
         <v>1581.5</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="11">
         <f>IF(C12=0, Parametri!$D$8, ABS(B12-C12)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -892,7 +905,7 @@
       <c r="E13" s="1">
         <v>1561</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="11">
         <f>IF(C13=0, Parametri!$D$8, ABS(B13-C13)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -925,7 +938,7 @@
       <c r="E14" s="1">
         <v>1533.5</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="11">
         <f>IF(C14=0, Parametri!$D$8, ABS(B14-C14)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -958,7 +971,7 @@
       <c r="E15" s="1">
         <v>1510.5</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="11">
         <f>IF(C15=0, Parametri!$D$8, ABS(B15-C15)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -991,7 +1004,7 @@
       <c r="E16" s="1">
         <v>1486.5</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="11">
         <f>IF(C16=0, Parametri!$D$8, ABS(B16-C16)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1024,7 +1037,7 @@
       <c r="E17" s="1">
         <v>1462</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="11">
         <f>IF(C17=0, Parametri!$D$8, ABS(B17-C17)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1057,7 +1070,7 @@
       <c r="E18" s="1">
         <v>1442.5</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="11">
         <f>IF(C18=0, Parametri!$D$8, ABS(B18-C18)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1090,7 +1103,7 @@
       <c r="E19" s="1">
         <v>1421</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="11">
         <f>IF(C19=0, Parametri!$D$8, ABS(B19-C19)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1123,7 +1136,7 @@
       <c r="E20" s="1">
         <v>1408.5</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="11">
         <f>IF(C20=0, Parametri!$D$8, ABS(B20-C20)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1156,7 +1169,7 @@
       <c r="E21" s="1">
         <v>1380</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="11">
         <f>IF(C21=0, Parametri!$D$8, ABS(B21-C21)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1189,7 +1202,7 @@
       <c r="E22" s="1">
         <v>1373.5</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="11">
         <f>IF(C22=0, Parametri!$D$8, ABS(B22-C22)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1222,7 +1235,7 @@
       <c r="E23" s="1">
         <v>1349</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="11">
         <f>IF(C23=0, Parametri!$D$8, ABS(B23-C23)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1255,7 +1268,7 @@
       <c r="E24" s="1">
         <v>1333.5</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="11">
         <f>IF(C24=0, Parametri!$D$8, ABS(B24-C24)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1288,7 +1301,7 @@
       <c r="E25" s="1">
         <v>1312.5</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="11">
         <f>IF(C25=0, Parametri!$D$8, ABS(B25-C25)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1321,7 +1334,7 @@
       <c r="E26" s="1">
         <v>1304</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="11">
         <f>IF(C26=0, Parametri!$D$8, ABS(B26-C26)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1354,7 +1367,7 @@
       <c r="E27" s="1">
         <v>1293</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="11">
         <f>IF(C27=0, Parametri!$D$8, ABS(B27-C27)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1387,7 +1400,7 @@
       <c r="E28" s="1">
         <v>1274</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="11">
         <f>IF(C28=0, Parametri!$D$8, ABS(B28-C28)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1420,7 +1433,7 @@
       <c r="E29" s="1">
         <v>1260</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="11">
         <f>IF(C29=0, Parametri!$D$8, ABS(B29-C29)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1453,7 +1466,7 @@
       <c r="E30" s="1">
         <v>1245.5</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="11">
         <f>IF(C30=0, Parametri!$D$8, ABS(B30-C30)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1486,7 +1499,7 @@
       <c r="E31" s="1">
         <v>1232</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="11">
         <f>IF(C31=0, Parametri!$D$8, ABS(B31-C31)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1519,7 +1532,7 @@
       <c r="E32" s="1">
         <v>1213.5</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="11">
         <f>IF(C32=0, Parametri!$D$8, ABS(B32-C32)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1552,7 +1565,7 @@
       <c r="E33" s="1">
         <v>1209.5</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="11">
         <f>IF(C33=0, Parametri!$D$8, ABS(B33-C33)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1585,7 +1598,7 @@
       <c r="E34" s="1">
         <v>1199</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="11">
         <f>IF(C34=0, Parametri!$D$8, ABS(B34-C34)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1618,7 +1631,7 @@
       <c r="E35" s="1">
         <v>1188</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="11">
         <f>IF(C35=0, Parametri!$D$8, ABS(B35-C35)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1651,7 +1664,7 @@
       <c r="E36" s="1">
         <v>1178.5</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="11">
         <f>IF(C36=0, Parametri!$D$8, ABS(B36-C36)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1684,7 +1697,7 @@
       <c r="E37" s="1">
         <v>1166.5</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="11">
         <f>IF(C37=0, Parametri!$D$8, ABS(B37-C37)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1717,7 +1730,7 @@
       <c r="E38" s="1">
         <v>1155.5</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="11">
         <f>IF(C38=0, Parametri!$D$8, ABS(B38-C38)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1750,7 +1763,7 @@
       <c r="E39" s="1">
         <v>1141</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="11">
         <f>IF(C39=0, Parametri!$D$8, ABS(B39-C39)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1783,7 +1796,7 @@
       <c r="E40" s="1">
         <v>1138.5</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="11">
         <f>IF(C40=0, Parametri!$D$8, ABS(B40-C40)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1816,7 +1829,7 @@
       <c r="E41" s="1">
         <v>1128</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="11">
         <f>IF(C41=0, Parametri!$D$8, ABS(B41-C41)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1849,7 +1862,7 @@
       <c r="E42" s="1">
         <v>1116</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="11">
         <f>IF(C42=0, Parametri!$D$8, ABS(B42-C42)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1882,7 +1895,7 @@
       <c r="E43" s="1">
         <v>1110</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="11">
         <f>IF(C43=0, Parametri!$D$8, ABS(B43-C43)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1915,7 +1928,7 @@
       <c r="E44" s="1">
         <v>1097.5</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="11">
         <f>IF(C44=0, Parametri!$D$8, ABS(B44-C44)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1948,7 +1961,7 @@
       <c r="E45" s="1">
         <v>1092.5</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="11">
         <f>IF(C45=0, Parametri!$D$8, ABS(B45-C45)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -1981,7 +1994,7 @@
       <c r="E46" s="1">
         <v>1086.5</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="11">
         <f>IF(C46=0, Parametri!$D$8, ABS(B46-C46)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2014,7 +2027,7 @@
       <c r="E47" s="1">
         <v>1075</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="11">
         <f>IF(C47=0, Parametri!$D$8, ABS(B47-C47)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2047,7 +2060,7 @@
       <c r="E48" s="1">
         <v>1063</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="11">
         <f>IF(C48=0, Parametri!$D$8, ABS(B48-C48)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2080,7 +2093,7 @@
       <c r="E49" s="1">
         <v>1042.5</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="11">
         <f>IF(C49=0, Parametri!$D$8, ABS(B49-C49)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2113,7 +2126,7 @@
       <c r="E50" s="1">
         <v>1034</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="11">
         <f>IF(C50=0, Parametri!$D$8, ABS(B50-C50)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2146,7 +2159,7 @@
       <c r="E51" s="1">
         <v>1027.5</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="11">
         <f>IF(C51=0, Parametri!$D$8, ABS(B51-C51)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2179,7 +2192,7 @@
       <c r="E52" s="1">
         <v>1010</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="11">
         <f>IF(C52=0, Parametri!$D$8, ABS(B52-C52)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2212,7 +2225,7 @@
       <c r="E53" s="1">
         <v>999.5</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="11">
         <f>IF(C53=0, Parametri!$D$8, ABS(B53-C53)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2245,7 +2258,7 @@
       <c r="E54" s="1">
         <v>987.5</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="11">
         <f>IF(C54=0, Parametri!$D$8, ABS(B54-C54)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2278,7 +2291,7 @@
       <c r="E55" s="1">
         <v>980.5</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="11">
         <f>IF(C55=0, Parametri!$D$8, ABS(B55-C55)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2311,7 +2324,7 @@
       <c r="E56" s="1">
         <v>970</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="11">
         <f>IF(C56=0, Parametri!$D$8, ABS(B56-C56)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2344,7 +2357,7 @@
       <c r="E57" s="1">
         <v>955</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="11">
         <f>IF(C57=0, Parametri!$D$8, ABS(B57-C57)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2377,7 +2390,7 @@
       <c r="E58" s="1">
         <v>945.5</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="11">
         <f>IF(C58=0, Parametri!$D$8, ABS(B58-C58)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2410,7 +2423,7 @@
       <c r="E59" s="1">
         <v>943.5</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="11">
         <f>IF(C59=0, Parametri!$D$8, ABS(B59-C59)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2443,7 +2456,7 @@
       <c r="E60" s="1">
         <v>933.5</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="11">
         <f>IF(C60=0, Parametri!$D$8, ABS(B60-C60)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2476,7 +2489,7 @@
       <c r="E61" s="1">
         <v>931</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="11">
         <f>IF(C61=0, Parametri!$D$8, ABS(B61-C61)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2509,7 +2522,7 @@
       <c r="E62" s="1">
         <v>923</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="11">
         <f>IF(C62=0, Parametri!$D$8, ABS(B62-C62)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2542,7 +2555,7 @@
       <c r="E63" s="1">
         <v>920</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="11">
         <f>IF(C63=0, Parametri!$D$8, ABS(B63-C63)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2575,7 +2588,7 @@
       <c r="E64" s="1">
         <v>912</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="11">
         <f>IF(C64=0, Parametri!$D$8, ABS(B64-C64)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2608,7 +2621,7 @@
       <c r="E65" s="1">
         <v>906</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="11">
         <f>IF(C65=0, Parametri!$D$8, ABS(B65-C65)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2641,7 +2654,7 @@
       <c r="E66" s="1">
         <v>903</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="11">
         <f>IF(C66=0, Parametri!$D$8, ABS(B66-C66)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2674,7 +2687,7 @@
       <c r="E67" s="1">
         <v>891</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="11">
         <f>IF(C67=0, Parametri!$D$8, ABS(B67-C67)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2707,7 +2720,7 @@
       <c r="E68" s="1">
         <v>888.5</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="11">
         <f>IF(C68=0, Parametri!$D$8, ABS(B68-C68)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2740,7 +2753,7 @@
       <c r="E69" s="1">
         <v>890</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="11">
         <f>IF(C69=0, Parametri!$D$8, ABS(B69-C69)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2773,7 +2786,7 @@
       <c r="E70" s="1">
         <v>876</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="11">
         <f>IF(C70=0, Parametri!$D$8, ABS(B70-C70)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2806,7 +2819,7 @@
       <c r="E71" s="1">
         <v>872</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="11">
         <f>IF(C71=0, Parametri!$D$8, ABS(B71-C71)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2839,7 +2852,7 @@
       <c r="E72" s="1">
         <v>871</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="11">
         <f>IF(C72=0, Parametri!$D$8, ABS(B72-C72)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2872,7 +2885,7 @@
       <c r="E73" s="1">
         <v>867</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="11">
         <f>IF(C73=0, Parametri!$D$8, ABS(B73-C73)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2905,7 +2918,7 @@
       <c r="E74" s="1">
         <v>860.5</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="11">
         <f>IF(C74=0, Parametri!$D$8, ABS(B74-C74)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2938,7 +2951,7 @@
       <c r="E75" s="1">
         <v>860</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="11">
         <f>IF(C75=0, Parametri!$D$8, ABS(B75-C75)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -2971,7 +2984,7 @@
       <c r="E76" s="1">
         <v>853</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="11">
         <f>IF(C76=0, Parametri!$D$8, ABS(B76-C76)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3004,7 +3017,7 @@
       <c r="E77" s="1">
         <v>847.5</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="11">
         <f>IF(C77=0, Parametri!$D$8, ABS(B77-C77)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3037,7 +3050,7 @@
       <c r="E78" s="1">
         <v>848</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="11">
         <f>IF(C78=0, Parametri!$D$8, ABS(B78-C78)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3070,7 +3083,7 @@
       <c r="E79" s="1">
         <v>842.5</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="11">
         <f>IF(C79=0, Parametri!$D$8, ABS(B79-C79)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3103,7 +3116,7 @@
       <c r="E80" s="1">
         <v>841</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="11">
         <f>IF(C80=0, Parametri!$D$8, ABS(B80-C80)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3136,7 +3149,7 @@
       <c r="E81" s="1">
         <v>838.5</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="11">
         <f>IF(C81=0, Parametri!$D$8, ABS(B81-C81)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3169,7 +3182,7 @@
       <c r="E82" s="1">
         <v>841.5</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="11">
         <f>IF(C82=0, Parametri!$D$8, ABS(B82-C82)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3202,7 +3215,7 @@
       <c r="E83" s="1">
         <v>842</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="11">
         <f>IF(C83=0, Parametri!$D$8, ABS(B83-C83)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3235,7 +3248,7 @@
       <c r="E84" s="1">
         <v>841</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="11">
         <f>IF(C84=0, Parametri!$D$8, ABS(B84-C84)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3268,7 +3281,7 @@
       <c r="E85" s="1">
         <v>840.5</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="11">
         <f>IF(C85=0, Parametri!$D$8, ABS(B85-C85)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3301,7 +3314,7 @@
       <c r="E86" s="1">
         <v>840</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="11">
         <f>IF(C86=0, Parametri!$D$8, ABS(B86-C86)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3334,7 +3347,7 @@
       <c r="E87" s="1">
         <v>840</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="11">
         <f>IF(C87=0, Parametri!$D$8, ABS(B87-C87)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3367,7 +3380,7 @@
       <c r="E88" s="1">
         <v>840</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="11">
         <f>IF(C88=0, Parametri!$D$8, ABS(B88-C88)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3400,7 +3413,7 @@
       <c r="E89" s="1">
         <v>840</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="11">
         <f>IF(C89=0, Parametri!$D$8, ABS(B89-C89)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3433,7 +3446,7 @@
       <c r="E90" s="1">
         <v>840</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="11">
         <f>IF(C90=0, Parametri!$D$8, ABS(B90-C90)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3466,7 +3479,7 @@
       <c r="E91" s="1">
         <v>841.5</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="11">
         <f>IF(C91=0, Parametri!$D$8, ABS(B91-C91)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3499,7 +3512,7 @@
       <c r="E92" s="1">
         <v>846</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="11">
         <f>IF(C92=0, Parametri!$D$8, ABS(B92-C92)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3532,7 +3545,7 @@
       <c r="E93" s="1">
         <v>844.5</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="11">
         <f>IF(C93=0, Parametri!$D$8, ABS(B93-C93)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3565,7 +3578,7 @@
       <c r="E94" s="1">
         <v>850</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="11">
         <f>IF(C94=0, Parametri!$D$8, ABS(B94-C94)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3598,7 +3611,7 @@
       <c r="E95" s="1">
         <v>853</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="11">
         <f>IF(C95=0, Parametri!$D$8, ABS(B95-C95)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3631,7 +3644,7 @@
       <c r="E96" s="1">
         <v>856</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="11">
         <f>IF(C96=0, Parametri!$D$8, ABS(B96-C96)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3664,7 +3677,7 @@
       <c r="E97" s="1">
         <v>859</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="11">
         <f>IF(C97=0, Parametri!$D$8, ABS(B97-C97)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3697,7 +3710,7 @@
       <c r="E98" s="1">
         <v>858.5</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="11">
         <f>IF(C98=0, Parametri!$D$8, ABS(B98-C98)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3730,7 +3743,7 @@
       <c r="E99" s="1">
         <v>874.5</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="11">
         <f>IF(C99=0, Parametri!$D$8, ABS(B99-C99)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3763,7 +3776,7 @@
       <c r="E100" s="1">
         <v>876.5</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="11">
         <f>IF(C100=0, Parametri!$D$8, ABS(B100-C100)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3796,7 +3809,7 @@
       <c r="E101" s="1">
         <v>884</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="11">
         <f>IF(C101=0, Parametri!$D$8, ABS(B101-C101)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3829,7 +3842,7 @@
       <c r="E102" s="1">
         <v>889</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="11">
         <f>IF(C102=0, Parametri!$D$8, ABS(B102-C102)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3862,7 +3875,7 @@
       <c r="E103" s="1">
         <v>894.5</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="11">
         <f>IF(C103=0, Parametri!$D$8, ABS(B103-C103)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3895,7 +3908,7 @@
       <c r="E104" s="1">
         <v>906.5</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="11">
         <f>IF(C104=0, Parametri!$D$8, ABS(B104-C104)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3928,7 +3941,7 @@
       <c r="E105" s="1">
         <v>924.5</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="11">
         <f>IF(C105=0, Parametri!$D$8, ABS(B105-C105)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3961,7 +3974,7 @@
       <c r="E106" s="1">
         <v>937.5</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="11">
         <f>IF(C106=0, Parametri!$D$8, ABS(B106-C106)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -3994,7 +4007,7 @@
       <c r="E107" s="1">
         <v>952</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="11">
         <f>IF(C107=0, Parametri!$D$8, ABS(B107-C107)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4027,7 +4040,7 @@
       <c r="E108" s="1">
         <v>968.5</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="11">
         <f>IF(C108=0, Parametri!$D$8, ABS(B108-C108)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4060,7 +4073,7 @@
       <c r="E109" s="1">
         <v>984.5</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="11">
         <f>IF(C109=0, Parametri!$D$8, ABS(B109-C109)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4093,7 +4106,7 @@
       <c r="E110" s="1">
         <v>1001</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="11">
         <f>IF(C110=0, Parametri!$D$8, ABS(B110-C110)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4126,7 +4139,7 @@
       <c r="E111" s="1">
         <v>1017</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="11">
         <f>IF(C111=0, Parametri!$D$8, ABS(B111-C111)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4159,7 +4172,7 @@
       <c r="E112" s="1">
         <v>1033.5</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="11">
         <f>IF(C112=0, Parametri!$D$8, ABS(B112-C112)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4192,7 +4205,7 @@
       <c r="E113" s="1">
         <v>1050</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="11">
         <f>IF(C113=0, Parametri!$D$8, ABS(B113-C113)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4225,7 +4238,7 @@
       <c r="E114" s="1">
         <v>1093.5</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="11">
         <f>IF(C114=0, Parametri!$D$8, ABS(B114-C114)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4258,7 +4271,7 @@
       <c r="E115" s="1">
         <v>1138</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="11">
         <f>IF(C115=0, Parametri!$D$8, ABS(B115-C115)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4291,7 +4304,7 @@
       <c r="E116" s="1">
         <v>1184.5</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="11">
         <f>IF(C116=0, Parametri!$D$8, ABS(B116-C116)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4324,7 +4337,7 @@
       <c r="E117" s="1">
         <v>1228</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="11">
         <f>IF(C117=0, Parametri!$D$8, ABS(B117-C117)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4357,7 +4370,7 @@
       <c r="E118" s="1">
         <v>1275</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="11">
         <f>IF(C118=0, Parametri!$D$8, ABS(B118-C118)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4390,7 +4403,7 @@
       <c r="E119" s="1">
         <v>1323</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="11">
         <f>IF(C119=0, Parametri!$D$8, ABS(B119-C119)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4423,7 +4436,7 @@
       <c r="E120" s="1">
         <v>1418</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="11">
         <f>IF(C120=0, Parametri!$D$8, ABS(B120-C120)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4456,7 +4469,7 @@
       <c r="E121" s="1">
         <v>1510</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="11">
         <f>IF(C121=0, Parametri!$D$8, ABS(B121-C121)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4489,7 +4502,7 @@
       <c r="E122" s="1">
         <v>1609</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="11">
         <f>IF(C122=0, Parametri!$D$8, ABS(B122-C122)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4522,7 +4535,7 @@
       <c r="E123" s="1">
         <v>1707</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="11">
         <f>IF(C123=0, Parametri!$D$8, ABS(B123-C123)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4555,7 +4568,7 @@
       <c r="E124" s="1">
         <v>1803</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="11">
         <f>IF(C124=0, Parametri!$D$8, ABS(B124-C124)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -4588,7 +4601,7 @@
       <c r="E125" s="1">
         <v>1902</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="11">
         <f>IF(C125=0, Parametri!$D$8, ABS(B125-C125)/(2*SQRT(3)))</f>
         <v>0.11547005383792516</v>
       </c>
@@ -6451,8 +6464,8 @@
       <c r="D63" s="8">
         <v>886</v>
       </c>
-      <c r="E63" s="8">
-        <v>255.76616925100421</v>
+      <c r="E63" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F63" s="1">
         <v>316.5</v>
@@ -6460,8 +6473,8 @@
       <c r="G63" s="8">
         <v>549</v>
       </c>
-      <c r="H63" s="1">
-        <v>255.76616925100421</v>
+      <c r="H63" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I63" s="1">
         <v>0.11547005383792516</v>
@@ -6477,8 +6490,8 @@
       <c r="D64" s="8">
         <v>871</v>
       </c>
-      <c r="E64" s="8">
-        <v>251.43604223208203</v>
+      <c r="E64" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F64" s="1">
         <v>321.5</v>
@@ -6486,8 +6499,8 @@
       <c r="G64" s="8">
         <v>529</v>
       </c>
-      <c r="H64" s="1">
-        <v>251.43604223208203</v>
+      <c r="H64" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I64" s="1">
         <v>0.11547005383792516</v>
@@ -6503,8 +6516,8 @@
       <c r="D65" s="8">
         <v>870</v>
       </c>
-      <c r="E65" s="8">
-        <v>251.14736709748723</v>
+      <c r="E65" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F65" s="1">
         <v>326.5</v>
@@ -6512,8 +6525,8 @@
       <c r="G65" s="8">
         <v>523</v>
       </c>
-      <c r="H65" s="1">
-        <v>251.14736709748723</v>
+      <c r="H65" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I65" s="1">
         <v>0.11547005383792516</v>
@@ -6529,8 +6542,8 @@
       <c r="D66" s="8">
         <v>864</v>
       </c>
-      <c r="E66" s="8">
-        <v>249.41531628991834</v>
+      <c r="E66" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F66" s="1">
         <v>331.5</v>
@@ -6538,8 +6551,8 @@
       <c r="G66" s="8">
         <v>512</v>
       </c>
-      <c r="H66" s="1">
-        <v>249.41531628991834</v>
+      <c r="H66" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I66" s="1">
         <v>0.11547005383792516</v>
@@ -6555,8 +6568,8 @@
       <c r="D67" s="8">
         <v>856</v>
       </c>
-      <c r="E67" s="8">
-        <v>247.10591521315985</v>
+      <c r="E67" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F67" s="1">
         <v>336.5</v>
@@ -6564,8 +6577,8 @@
       <c r="G67" s="8">
         <v>499</v>
       </c>
-      <c r="H67" s="1">
-        <v>247.10591521315985</v>
+      <c r="H67" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I67" s="1">
         <v>0.11547005383792516</v>
@@ -6581,8 +6594,8 @@
       <c r="D68" s="8">
         <v>851</v>
       </c>
-      <c r="E68" s="8">
-        <v>245.66253954018578</v>
+      <c r="E68" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F68" s="1">
         <v>341.5</v>
@@ -6590,8 +6603,8 @@
       <c r="G68" s="8">
         <v>489</v>
       </c>
-      <c r="H68" s="1">
-        <v>245.66253954018578</v>
+      <c r="H68" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I68" s="1">
         <v>0.11547005383792516</v>
@@ -6607,8 +6620,8 @@
       <c r="D69" s="8">
         <v>846</v>
       </c>
-      <c r="E69" s="8">
-        <v>244.21916386721171</v>
+      <c r="E69" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F69" s="1">
         <v>346.5</v>
@@ -6616,8 +6629,8 @@
       <c r="G69" s="8">
         <v>479</v>
       </c>
-      <c r="H69" s="1">
-        <v>244.21916386721171</v>
+      <c r="H69" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I69" s="1">
         <v>0.11547005383792516</v>
@@ -6633,8 +6646,8 @@
       <c r="D70" s="8">
         <v>840</v>
       </c>
-      <c r="E70" s="8">
-        <v>242.48711305964284</v>
+      <c r="E70" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F70" s="1">
         <v>351.5</v>
@@ -6642,8 +6655,8 @@
       <c r="G70" s="8">
         <v>468</v>
       </c>
-      <c r="H70" s="1">
-        <v>242.48711305964284</v>
+      <c r="H70" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I70" s="1">
         <v>0.11547005383792516</v>
@@ -6659,8 +6672,8 @@
       <c r="D71" s="8">
         <v>835</v>
       </c>
-      <c r="E71" s="8">
-        <v>241.04373738666877</v>
+      <c r="E71" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F71" s="1">
         <v>356.5</v>
@@ -6668,8 +6681,8 @@
       <c r="G71" s="8">
         <v>458</v>
       </c>
-      <c r="H71" s="1">
-        <v>241.04373738666877</v>
+      <c r="H71" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I71" s="1">
         <v>0.11547005383792516</v>
@@ -6685,8 +6698,8 @@
       <c r="D72" s="8">
         <v>833</v>
       </c>
-      <c r="E72" s="8">
-        <v>240.46638711747914</v>
+      <c r="E72" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F72" s="1">
         <v>361.5</v>
@@ -6694,8 +6707,8 @@
       <c r="G72" s="8">
         <v>451</v>
       </c>
-      <c r="H72" s="1">
-        <v>240.46638711747914</v>
+      <c r="H72" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I72" s="1">
         <v>0.11547005383792516</v>
@@ -6711,8 +6724,8 @@
       <c r="D73" s="8">
         <v>832</v>
       </c>
-      <c r="E73" s="8">
-        <v>240.17771198288432</v>
+      <c r="E73" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F73" s="1">
         <v>366.5</v>
@@ -6720,8 +6733,8 @@
       <c r="G73" s="8">
         <v>445</v>
       </c>
-      <c r="H73" s="1">
-        <v>240.17771198288432</v>
+      <c r="H73" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I73" s="1">
         <v>0.11547005383792516</v>
@@ -6737,8 +6750,8 @@
       <c r="D74" s="8">
         <v>828</v>
       </c>
-      <c r="E74" s="8">
-        <v>239.02301144450507</v>
+      <c r="E74" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F74" s="1">
         <v>371.5</v>
@@ -6746,8 +6759,8 @@
       <c r="G74" s="8">
         <v>436</v>
       </c>
-      <c r="H74" s="1">
-        <v>239.02301144450507</v>
+      <c r="H74" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I74" s="1">
         <v>0.11547005383792516</v>
@@ -6763,8 +6776,8 @@
       <c r="D75" s="8">
         <v>825</v>
       </c>
-      <c r="E75" s="8">
-        <v>238.15698604072065</v>
+      <c r="E75" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F75" s="1">
         <v>376.5</v>
@@ -6772,8 +6785,8 @@
       <c r="G75" s="8">
         <v>428</v>
       </c>
-      <c r="H75" s="1">
-        <v>238.15698604072065</v>
+      <c r="H75" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I75" s="1">
         <v>0.11547005383792516</v>
@@ -6789,8 +6802,8 @@
       <c r="D76" s="8">
         <v>822</v>
       </c>
-      <c r="E76" s="8">
-        <v>237.29096063693621</v>
+      <c r="E76" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F76" s="1">
         <v>381.5</v>
@@ -6798,8 +6811,8 @@
       <c r="G76" s="8">
         <v>420</v>
       </c>
-      <c r="H76" s="1">
-        <v>237.29096063693621</v>
+      <c r="H76" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I76" s="1">
         <v>0.11547005383792516</v>
@@ -6815,8 +6828,8 @@
       <c r="D77" s="8">
         <v>820</v>
       </c>
-      <c r="E77" s="8">
-        <v>236.71361036774658</v>
+      <c r="E77" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F77" s="1">
         <v>386.5</v>
@@ -6824,8 +6837,8 @@
       <c r="G77" s="8">
         <v>413</v>
       </c>
-      <c r="H77" s="1">
-        <v>236.71361036774658</v>
+      <c r="H77" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I77" s="1">
         <v>0.11547005383792516</v>
@@ -6841,8 +6854,8 @@
       <c r="D78" s="8">
         <v>816</v>
       </c>
-      <c r="E78" s="8">
-        <v>235.55890982936734</v>
+      <c r="E78" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F78" s="1">
         <v>391.5</v>
@@ -6850,8 +6863,8 @@
       <c r="G78" s="8">
         <v>404</v>
       </c>
-      <c r="H78" s="1">
-        <v>235.55890982936734</v>
+      <c r="H78" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I78" s="1">
         <v>0.11547005383792516</v>
@@ -6867,8 +6880,8 @@
       <c r="D79" s="8">
         <v>814</v>
       </c>
-      <c r="E79" s="8">
-        <v>234.98155956017769</v>
+      <c r="E79" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F79" s="1">
         <v>396.5</v>
@@ -6876,8 +6889,8 @@
       <c r="G79" s="8">
         <v>397</v>
       </c>
-      <c r="H79" s="1">
-        <v>234.98155956017769</v>
+      <c r="H79" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I79" s="1">
         <v>0.11547005383792516</v>
@@ -6893,8 +6906,8 @@
       <c r="D80" s="8">
         <v>822</v>
       </c>
-      <c r="E80" s="8">
-        <v>237.29096063693621</v>
+      <c r="E80" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F80" s="1">
         <v>401.5</v>
@@ -6902,8 +6915,8 @@
       <c r="G80" s="8">
         <v>400</v>
       </c>
-      <c r="H80" s="1">
-        <v>237.29096063693621</v>
+      <c r="H80" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I80" s="1">
         <v>0.11547005383792516</v>
@@ -6919,8 +6932,8 @@
       <c r="D81" s="8">
         <v>825</v>
       </c>
-      <c r="E81" s="8">
-        <v>238.15698604072065</v>
+      <c r="E81" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F81" s="1">
         <v>406.5</v>
@@ -6928,8 +6941,8 @@
       <c r="G81" s="8">
         <v>398</v>
       </c>
-      <c r="H81" s="1">
-        <v>238.15698604072065</v>
+      <c r="H81" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I81" s="1">
         <v>0.11547005383792516</v>
@@ -6945,8 +6958,8 @@
       <c r="D82" s="8">
         <v>827</v>
       </c>
-      <c r="E82" s="8">
-        <v>238.73433630991028</v>
+      <c r="E82" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F82" s="1">
         <v>411.5</v>
@@ -6954,8 +6967,8 @@
       <c r="G82" s="8">
         <v>395</v>
       </c>
-      <c r="H82" s="1">
-        <v>238.73433630991028</v>
+      <c r="H82" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I82" s="1">
         <v>0.11547005383792516</v>
@@ -6971,8 +6984,8 @@
       <c r="D83" s="8">
         <v>827</v>
       </c>
-      <c r="E83" s="8">
-        <v>238.73433630991028</v>
+      <c r="E83" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F83" s="1">
         <v>416.5</v>
@@ -6980,8 +6993,8 @@
       <c r="G83" s="8">
         <v>390</v>
       </c>
-      <c r="H83" s="1">
-        <v>238.73433630991028</v>
+      <c r="H83" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I83" s="1">
         <v>0.11547005383792516</v>
@@ -6997,8 +7010,8 @@
       <c r="D84" s="8">
         <v>829</v>
       </c>
-      <c r="E84" s="8">
-        <v>239.3116865790999</v>
+      <c r="E84" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F84" s="1">
         <v>421.5</v>
@@ -7006,8 +7019,8 @@
       <c r="G84" s="8">
         <v>387</v>
       </c>
-      <c r="H84" s="1">
-        <v>239.3116865790999</v>
+      <c r="H84" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I84" s="1">
         <v>0.11547005383792516</v>
@@ -7023,8 +7036,8 @@
       <c r="D85" s="8">
         <v>830</v>
       </c>
-      <c r="E85" s="8">
-        <v>239.6003617136947</v>
+      <c r="E85" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F85" s="1">
         <v>426.5</v>
@@ -7032,8 +7045,8 @@
       <c r="G85" s="8">
         <v>383</v>
       </c>
-      <c r="H85" s="1">
-        <v>239.6003617136947</v>
+      <c r="H85" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I85" s="1">
         <v>0.11547005383792516</v>
@@ -7049,8 +7062,8 @@
       <c r="D86" s="8">
         <v>831</v>
       </c>
-      <c r="E86" s="8">
-        <v>239.88903684828952</v>
+      <c r="E86" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F86" s="1">
         <v>431.5</v>
@@ -7058,8 +7071,8 @@
       <c r="G86" s="8">
         <v>379</v>
       </c>
-      <c r="H86" s="1">
-        <v>239.88903684828952</v>
+      <c r="H86" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I86" s="1">
         <v>0.11547005383792516</v>
@@ -7075,8 +7088,8 @@
       <c r="D87" s="8">
         <v>832</v>
       </c>
-      <c r="E87" s="8">
-        <v>240.17771198288432</v>
+      <c r="E87" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F87" s="1">
         <v>441.5</v>
@@ -7084,8 +7097,8 @@
       <c r="G87" s="8">
         <v>370</v>
       </c>
-      <c r="H87" s="1">
-        <v>240.17771198288432</v>
+      <c r="H87" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I87" s="1">
         <v>0.11547005383792516</v>
@@ -7101,8 +7114,8 @@
       <c r="D88" s="8">
         <v>837</v>
       </c>
-      <c r="E88" s="8">
-        <v>241.62108765585839</v>
+      <c r="E88" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F88" s="1">
         <v>451.5</v>
@@ -7110,8 +7123,8 @@
       <c r="G88" s="8">
         <v>365</v>
       </c>
-      <c r="H88" s="1">
-        <v>241.62108765585839</v>
+      <c r="H88" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I88" s="1">
         <v>0.11547005383792516</v>
@@ -7127,8 +7140,8 @@
       <c r="D89" s="8">
         <v>840</v>
       </c>
-      <c r="E89" s="8">
-        <v>242.48711305964284</v>
+      <c r="E89" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F89" s="1">
         <v>461.5</v>
@@ -7136,8 +7149,8 @@
       <c r="G89" s="8">
         <v>358</v>
       </c>
-      <c r="H89" s="1">
-        <v>242.48711305964284</v>
+      <c r="H89" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I89" s="1">
         <v>0.11547005383792516</v>
@@ -7153,8 +7166,8 @@
       <c r="D90" s="8">
         <v>835</v>
       </c>
-      <c r="E90" s="8">
-        <v>241.04373738666877</v>
+      <c r="E90" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F90" s="1">
         <v>471.5</v>
@@ -7162,8 +7175,8 @@
       <c r="G90" s="8">
         <v>343</v>
       </c>
-      <c r="H90" s="1">
-        <v>241.04373738666877</v>
+      <c r="H90" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I90" s="1">
         <v>0.11547005383792516</v>
@@ -7179,8 +7192,8 @@
       <c r="D91" s="8">
         <v>850</v>
       </c>
-      <c r="E91" s="8">
-        <v>245.37386440559095</v>
+      <c r="E91" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F91" s="1">
         <v>481.5</v>
@@ -7188,8 +7201,8 @@
       <c r="G91" s="8">
         <v>348</v>
       </c>
-      <c r="H91" s="1">
-        <v>245.37386440559095</v>
+      <c r="H91" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I91" s="1">
         <v>0.11547005383792516</v>
@@ -7205,8 +7218,8 @@
       <c r="D92" s="8">
         <v>855</v>
       </c>
-      <c r="E92" s="8">
-        <v>246.81724007856502</v>
+      <c r="E92" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F92" s="1">
         <v>491.5</v>
@@ -7214,8 +7227,8 @@
       <c r="G92" s="8">
         <v>343</v>
       </c>
-      <c r="H92" s="1">
-        <v>246.81724007856502</v>
+      <c r="H92" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I92" s="1">
         <v>0.11547005383792516</v>
@@ -7231,8 +7244,8 @@
       <c r="D93" s="8">
         <v>860</v>
       </c>
-      <c r="E93" s="8">
-        <v>248.26061575153909</v>
+      <c r="E93" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F93" s="1">
         <v>501.5</v>
@@ -7240,8 +7253,8 @@
       <c r="G93" s="8">
         <v>338</v>
       </c>
-      <c r="H93" s="1">
-        <v>248.26061575153909</v>
+      <c r="H93" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I93" s="1">
         <v>0.11547005383792516</v>
@@ -7257,8 +7270,8 @@
       <c r="D94" s="8">
         <v>865</v>
       </c>
-      <c r="E94" s="8">
-        <v>249.70399142451316</v>
+      <c r="E94" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F94" s="1">
         <v>511.5</v>
@@ -7266,8 +7279,8 @@
       <c r="G94" s="8">
         <v>333</v>
       </c>
-      <c r="H94" s="1">
-        <v>249.70399142451316</v>
+      <c r="H94" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I94" s="1">
         <v>0.11547005383792516</v>
@@ -7283,8 +7296,8 @@
       <c r="D95" s="8">
         <v>870</v>
       </c>
-      <c r="E95" s="8">
-        <v>251.14736709748723</v>
+      <c r="E95" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F95" s="1">
         <v>521.5</v>
@@ -7292,8 +7305,8 @@
       <c r="G95" s="8">
         <v>328</v>
       </c>
-      <c r="H95" s="1">
-        <v>251.14736709748723</v>
+      <c r="H95" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I95" s="1">
         <v>0.11547005383792516</v>
@@ -7309,8 +7322,8 @@
       <c r="D96" s="8">
         <v>875</v>
       </c>
-      <c r="E96" s="8">
-        <v>252.59074277046128</v>
+      <c r="E96" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F96" s="1">
         <v>531.5</v>
@@ -7318,8 +7331,8 @@
       <c r="G96" s="8">
         <v>323</v>
       </c>
-      <c r="H96" s="1">
-        <v>252.59074277046128</v>
+      <c r="H96" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I96" s="1">
         <v>0.11547005383792516</v>
@@ -7335,8 +7348,8 @@
       <c r="D97" s="8">
         <v>885</v>
       </c>
-      <c r="E97" s="8">
-        <v>255.47749411640942</v>
+      <c r="E97" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F97" s="1">
         <v>541.5</v>
@@ -7344,8 +7357,8 @@
       <c r="G97" s="8">
         <v>323</v>
       </c>
-      <c r="H97" s="1">
-        <v>255.47749411640942</v>
+      <c r="H97" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I97" s="1">
         <v>0.11547005383792516</v>
@@ -7361,8 +7374,8 @@
       <c r="D98" s="8">
         <v>890</v>
       </c>
-      <c r="E98" s="8">
-        <v>256.92086978938346</v>
+      <c r="E98" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F98" s="1">
         <v>551.5</v>
@@ -7370,8 +7383,8 @@
       <c r="G98" s="8">
         <v>318</v>
       </c>
-      <c r="H98" s="1">
-        <v>256.92086978938346</v>
+      <c r="H98" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I98" s="1">
         <v>0.11547005383792516</v>
@@ -7387,8 +7400,8 @@
       <c r="D99" s="8">
         <v>897</v>
       </c>
-      <c r="E99" s="8">
-        <v>258.94159573154718</v>
+      <c r="E99" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F99" s="1">
         <v>561.5</v>
@@ -7396,8 +7409,8 @@
       <c r="G99" s="8">
         <v>315</v>
       </c>
-      <c r="H99" s="1">
-        <v>258.94159573154718</v>
+      <c r="H99" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I99" s="1">
         <v>0.11547005383792516</v>
@@ -7413,8 +7426,8 @@
       <c r="D100" s="8">
         <v>905</v>
       </c>
-      <c r="E100" s="8">
-        <v>261.25099680830567</v>
+      <c r="E100" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F100" s="1">
         <v>571.5</v>
@@ -7422,8 +7435,8 @@
       <c r="G100" s="8">
         <v>313</v>
       </c>
-      <c r="H100" s="1">
-        <v>261.25099680830567</v>
+      <c r="H100" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I100" s="1">
         <v>0.11547005383792516</v>
@@ -7439,8 +7452,8 @@
       <c r="D101" s="8">
         <v>910</v>
       </c>
-      <c r="E101" s="8">
-        <v>262.69437248127974</v>
+      <c r="E101" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F101" s="1">
         <v>581.5</v>
@@ -7448,8 +7461,8 @@
       <c r="G101" s="8">
         <v>308</v>
       </c>
-      <c r="H101" s="1">
-        <v>262.69437248127974</v>
+      <c r="H101" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I101" s="1">
         <v>0.11547005383792516</v>
@@ -7465,8 +7478,8 @@
       <c r="D102" s="8">
         <v>925</v>
       </c>
-      <c r="E102" s="8">
-        <v>267.02449950020196</v>
+      <c r="E102" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F102" s="1">
         <v>601.5</v>
@@ -7474,8 +7487,8 @@
       <c r="G102" s="8">
         <v>303</v>
       </c>
-      <c r="H102" s="1">
-        <v>267.02449950020196</v>
+      <c r="H102" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I102" s="1">
         <v>0.11547005383792516</v>
@@ -7491,8 +7504,8 @@
       <c r="D103" s="8">
         <v>939</v>
       </c>
-      <c r="E103" s="8">
-        <v>271.06595138452928</v>
+      <c r="E103" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F103" s="1">
         <v>621.5</v>
@@ -7500,8 +7513,8 @@
       <c r="G103" s="8">
         <v>297</v>
       </c>
-      <c r="H103" s="1">
-        <v>271.06595138452928</v>
+      <c r="H103" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I103" s="1">
         <v>0.11547005383792516</v>
@@ -7517,8 +7530,8 @@
       <c r="D104" s="8">
         <v>958</v>
       </c>
-      <c r="E104" s="8">
-        <v>276.55077894183074</v>
+      <c r="E104" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F104" s="1">
         <v>641.5</v>
@@ -7526,8 +7539,8 @@
       <c r="G104" s="8">
         <v>296</v>
       </c>
-      <c r="H104" s="1">
-        <v>276.55077894183074</v>
+      <c r="H104" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I104" s="1">
         <v>0.11547005383792516</v>
@@ -7543,8 +7556,8 @@
       <c r="D105" s="8">
         <v>972</v>
       </c>
-      <c r="E105" s="8">
-        <v>280.59223082615813</v>
+      <c r="E105" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F105" s="1">
         <v>661.5</v>
@@ -7552,8 +7565,8 @@
       <c r="G105" s="8">
         <v>290</v>
       </c>
-      <c r="H105" s="1">
-        <v>280.59223082615813</v>
+      <c r="H105" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I105" s="1">
         <v>0.11547005383792516</v>
@@ -7569,8 +7582,8 @@
       <c r="D106" s="8">
         <v>990</v>
       </c>
-      <c r="E106" s="8">
-        <v>285.78838324886476</v>
+      <c r="E106" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F106" s="1">
         <v>681.5</v>
@@ -7578,8 +7591,8 @@
       <c r="G106" s="8">
         <v>288</v>
       </c>
-      <c r="H106" s="1">
-        <v>285.78838324886476</v>
+      <c r="H106" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I106" s="1">
         <v>0.11547005383792516</v>
@@ -7595,8 +7608,8 @@
       <c r="D107" s="8">
         <v>1030</v>
       </c>
-      <c r="E107" s="8">
-        <v>297.33538863265727</v>
+      <c r="E107" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F107" s="1">
         <v>731.5</v>
@@ -7604,8 +7617,8 @@
       <c r="G107" s="8">
         <v>278</v>
       </c>
-      <c r="H107" s="1">
-        <v>297.33538863265727</v>
+      <c r="H107" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I107" s="1">
         <v>0.11547005383792516</v>
@@ -7621,8 +7634,8 @@
       <c r="D108" s="8">
         <v>1073</v>
       </c>
-      <c r="E108" s="8">
-        <v>309.74841942023426</v>
+      <c r="E108" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F108" s="1">
         <v>781.5</v>
@@ -7630,8 +7643,8 @@
       <c r="G108" s="8">
         <v>271</v>
       </c>
-      <c r="H108" s="1">
-        <v>309.74841942023426</v>
+      <c r="H108" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I108" s="1">
         <v>0.11547005383792516</v>
@@ -7647,8 +7660,8 @@
       <c r="D109" s="8">
         <v>1118</v>
       </c>
-      <c r="E109" s="8">
-        <v>322.73880047700084</v>
+      <c r="E109" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F109" s="1">
         <v>831.5</v>
@@ -7656,8 +7669,8 @@
       <c r="G109" s="8">
         <v>266</v>
       </c>
-      <c r="H109" s="1">
-        <v>322.73880047700084</v>
+      <c r="H109" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I109" s="1">
         <v>0.11547005383792516</v>
@@ -7673,8 +7686,8 @@
       <c r="D110" s="8">
         <v>1164</v>
       </c>
-      <c r="E110" s="8">
-        <v>336.01785666836224</v>
+      <c r="E110" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F110" s="1">
         <v>881.5</v>
@@ -7682,8 +7695,8 @@
       <c r="G110" s="8">
         <v>262</v>
       </c>
-      <c r="H110" s="1">
-        <v>336.01785666836224</v>
+      <c r="H110" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I110" s="1">
         <v>0.11547005383792516</v>
@@ -7699,8 +7712,8 @@
       <c r="D111" s="8">
         <v>1255</v>
       </c>
-      <c r="E111" s="8">
-        <v>362.28729391649017</v>
+      <c r="E111" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F111" s="1">
         <v>981.5</v>
@@ -7708,8 +7721,8 @@
       <c r="G111" s="8">
         <v>253</v>
       </c>
-      <c r="H111" s="1">
-        <v>362.28729391649017</v>
+      <c r="H111" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I111" s="1">
         <v>0.11547005383792516</v>
@@ -7725,8 +7738,8 @@
       <c r="D112" s="8">
         <v>1349</v>
       </c>
-      <c r="E112" s="8">
-        <v>389.42275656840258</v>
+      <c r="E112" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F112" s="1">
         <v>1081.5</v>
@@ -7734,8 +7747,8 @@
       <c r="G112" s="8">
         <v>247</v>
       </c>
-      <c r="H112" s="1">
-        <v>389.42275656840258</v>
+      <c r="H112" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I112" s="1">
         <v>0.11547005383792516</v>
@@ -7751,8 +7764,8 @@
       <c r="D113" s="8">
         <v>1445</v>
       </c>
-      <c r="E113" s="8">
-        <v>417.13556948950463</v>
+      <c r="E113" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F113" s="1">
         <v>1181.5</v>
@@ -7760,8 +7773,8 @@
       <c r="G113" s="8">
         <v>243</v>
       </c>
-      <c r="H113" s="1">
-        <v>417.13556948950463</v>
+      <c r="H113" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I113" s="1">
         <v>0.11547005383792516</v>
@@ -7777,8 +7790,8 @@
       <c r="D114" s="8">
         <v>1542</v>
       </c>
-      <c r="E114" s="8">
-        <v>445.13705754520151</v>
+      <c r="E114" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F114" s="1">
         <v>1281.5</v>
@@ -7786,8 +7799,8 @@
       <c r="G114" s="8">
         <v>240</v>
       </c>
-      <c r="H114" s="1">
-        <v>445.13705754520151</v>
+      <c r="H114" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I114" s="1">
         <v>0.11547005383792516</v>
@@ -7803,8 +7816,8 @@
       <c r="D115" s="8">
         <v>1638</v>
       </c>
-      <c r="E115" s="8">
-        <v>472.84987046630351</v>
+      <c r="E115" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F115" s="1">
         <v>1381.5</v>
@@ -7812,8 +7825,8 @@
       <c r="G115" s="8">
         <v>236</v>
       </c>
-      <c r="H115" s="1">
-        <v>472.84987046630351</v>
+      <c r="H115" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I115" s="1">
         <v>0.11547005383792516</v>
@@ -7829,8 +7842,8 @@
       <c r="D116" s="8">
         <v>1736</v>
       </c>
-      <c r="E116" s="8">
-        <v>501.14003365659516</v>
+      <c r="E116" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F116" s="1">
         <v>1481.5</v>
@@ -7838,8 +7851,8 @@
       <c r="G116" s="8">
         <v>234</v>
       </c>
-      <c r="H116" s="1">
-        <v>501.14003365659516</v>
+      <c r="H116" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I116" s="1">
         <v>0.11547005383792516</v>
@@ -7855,8 +7868,8 @@
       <c r="D117" s="8">
         <v>1882</v>
       </c>
-      <c r="E117" s="8">
-        <v>543.28660330743787</v>
+      <c r="E117" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="F117" s="1">
         <v>1631.5</v>
@@ -7864,8 +7877,8 @@
       <c r="G117" s="8">
         <v>230</v>
       </c>
-      <c r="H117" s="1">
-        <v>543.28660330743787</v>
+      <c r="H117" s="9">
+        <v>0.11547005383792516</v>
       </c>
       <c r="I117" s="1">
         <v>0.11547005383792516</v>

--- a/Laboratorio/esperienza2/esperienza2.xlsx
+++ b/Laboratorio/esperienza2/esperienza2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michele/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\Documents\UNIVERSITA'\III ANNO\Laboratorio-di-Ottica\Laboratorio\esperienza2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D9BD58-CF2D-1D45-98A9-42808ECA812B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C6A893-9E1E-4D6A-9933-327821FCC105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8840" yWindow="3340" windowWidth="25360" windowHeight="15000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -114,8 +114,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="#,##0.000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -126,12 +126,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -161,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -183,16 +189,29 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -383,13 +402,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5" customWidth="1"/>
-    <col min="2" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="4" width="12.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -400,13 +419,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -417,13 +436,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -437,7 +456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="4">
         <v>0.2</v>
@@ -451,8 +470,8 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -466,7 +485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="4">
         <v>0.2</v>
@@ -489,17 +508,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J130"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="5" customWidth="1"/>
-    <col min="2" max="3" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="10" customWidth="1"/>
-    <col min="7" max="10" width="12.5" style="5" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="5" customWidth="1"/>
+    <col min="2" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="10" customWidth="1"/>
+    <col min="7" max="10" width="12.44140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
@@ -531,7 +550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>270</v>
       </c>
@@ -563,7 +582,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <f t="shared" ref="A3:A47" si="2">A2+1</f>
         <v>271</v>
@@ -596,7 +615,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <f t="shared" si="2"/>
         <v>272</v>
@@ -629,7 +648,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <f t="shared" si="2"/>
         <v>273</v>
@@ -662,7 +681,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <f t="shared" si="2"/>
         <v>274</v>
@@ -695,7 +714,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <f t="shared" si="2"/>
         <v>275</v>
@@ -728,7 +747,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <f t="shared" si="2"/>
         <v>276</v>
@@ -761,7 +780,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <f t="shared" si="2"/>
         <v>277</v>
@@ -794,7 +813,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <f t="shared" si="2"/>
         <v>278</v>
@@ -827,7 +846,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <f t="shared" si="2"/>
         <v>279</v>
@@ -860,7 +879,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <f t="shared" si="2"/>
         <v>280</v>
@@ -893,7 +912,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <f t="shared" si="2"/>
         <v>281</v>
@@ -926,7 +945,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <f t="shared" si="2"/>
         <v>282</v>
@@ -959,7 +978,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <f t="shared" si="2"/>
         <v>283</v>
@@ -992,7 +1011,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <f t="shared" si="2"/>
         <v>284</v>
@@ -1025,7 +1044,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <f t="shared" si="2"/>
         <v>285</v>
@@ -1058,7 +1077,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <f t="shared" si="2"/>
         <v>286</v>
@@ -1091,7 +1110,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <f t="shared" si="2"/>
         <v>287</v>
@@ -1124,7 +1143,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <f t="shared" si="2"/>
         <v>288</v>
@@ -1157,7 +1176,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <f t="shared" si="2"/>
         <v>289</v>
@@ -1190,7 +1209,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <f t="shared" si="2"/>
         <v>290</v>
@@ -1223,7 +1242,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <f t="shared" si="2"/>
         <v>291</v>
@@ -1256,7 +1275,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <f t="shared" si="2"/>
         <v>292</v>
@@ -1289,7 +1308,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <f t="shared" si="2"/>
         <v>293</v>
@@ -1322,7 +1341,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <f t="shared" si="2"/>
         <v>294</v>
@@ -1355,7 +1374,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <f t="shared" si="2"/>
         <v>295</v>
@@ -1388,7 +1407,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <f t="shared" si="2"/>
         <v>296</v>
@@ -1421,7 +1440,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <f t="shared" si="2"/>
         <v>297</v>
@@ -1454,7 +1473,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <f t="shared" si="2"/>
         <v>298</v>
@@ -1487,7 +1506,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <f t="shared" si="2"/>
         <v>299</v>
@@ -1520,7 +1539,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <f t="shared" si="2"/>
         <v>300</v>
@@ -1553,7 +1572,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <f t="shared" si="2"/>
         <v>301</v>
@@ -1586,7 +1605,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <f t="shared" si="2"/>
         <v>302</v>
@@ -1619,7 +1638,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <f t="shared" si="2"/>
         <v>303</v>
@@ -1652,7 +1671,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <f t="shared" si="2"/>
         <v>304</v>
@@ -1685,7 +1704,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <f t="shared" si="2"/>
         <v>305</v>
@@ -1718,7 +1737,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <f t="shared" si="2"/>
         <v>306</v>
@@ -1751,7 +1770,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <f t="shared" si="2"/>
         <v>307</v>
@@ -1784,7 +1803,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <f t="shared" si="2"/>
         <v>308</v>
@@ -1817,7 +1836,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <f t="shared" si="2"/>
         <v>309</v>
@@ -1850,7 +1869,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <f t="shared" si="2"/>
         <v>310</v>
@@ -1883,7 +1902,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <f t="shared" si="2"/>
         <v>311</v>
@@ -1916,7 +1935,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <f t="shared" si="2"/>
         <v>312</v>
@@ -1949,7 +1968,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <f t="shared" si="2"/>
         <v>313</v>
@@ -1982,7 +2001,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <f t="shared" si="2"/>
         <v>314</v>
@@ -2015,7 +2034,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <f t="shared" si="2"/>
         <v>315</v>
@@ -2048,7 +2067,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <f t="shared" ref="A48:A65" si="5">A47+2</f>
         <v>317</v>
@@ -2081,7 +2100,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <f t="shared" si="5"/>
         <v>319</v>
@@ -2114,7 +2133,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <f t="shared" si="5"/>
         <v>321</v>
@@ -2147,7 +2166,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <f t="shared" si="5"/>
         <v>323</v>
@@ -2180,7 +2199,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <f t="shared" si="5"/>
         <v>325</v>
@@ -2213,7 +2232,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <f t="shared" si="5"/>
         <v>327</v>
@@ -2246,7 +2265,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -2279,7 +2298,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <f t="shared" si="5"/>
         <v>331</v>
@@ -2312,7 +2331,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <f t="shared" si="5"/>
         <v>333</v>
@@ -2345,7 +2364,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <f t="shared" si="5"/>
         <v>335</v>
@@ -2378,7 +2397,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <f t="shared" si="5"/>
         <v>337</v>
@@ -2411,7 +2430,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <f t="shared" si="5"/>
         <v>339</v>
@@ -2444,7 +2463,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <f t="shared" si="5"/>
         <v>341</v>
@@ -2477,7 +2496,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <f t="shared" si="5"/>
         <v>343</v>
@@ -2510,7 +2529,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <f t="shared" si="5"/>
         <v>345</v>
@@ -2543,7 +2562,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <f t="shared" si="5"/>
         <v>347</v>
@@ -2576,7 +2595,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <f t="shared" si="5"/>
         <v>349</v>
@@ -2609,7 +2628,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <f t="shared" si="5"/>
         <v>351</v>
@@ -2642,7 +2661,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <f t="shared" ref="A66:A73" si="6">A65+3</f>
         <v>354</v>
@@ -2675,7 +2694,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <f t="shared" si="6"/>
         <v>357</v>
@@ -2708,7 +2727,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <f t="shared" si="6"/>
         <v>360</v>
@@ -2741,7 +2760,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <f t="shared" si="6"/>
         <v>363</v>
@@ -2774,7 +2793,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <f t="shared" si="6"/>
         <v>366</v>
@@ -2807,7 +2826,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <f t="shared" si="6"/>
         <v>369</v>
@@ -2840,7 +2859,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <f t="shared" si="6"/>
         <v>372</v>
@@ -2873,7 +2892,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <f t="shared" si="6"/>
         <v>375</v>
@@ -2906,7 +2925,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <f t="shared" ref="A74:A81" si="9">A73+4</f>
         <v>379</v>
@@ -2939,7 +2958,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <f t="shared" si="9"/>
         <v>383</v>
@@ -2972,7 +2991,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <f t="shared" si="9"/>
         <v>387</v>
@@ -3005,7 +3024,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <f t="shared" si="9"/>
         <v>391</v>
@@ -3038,7 +3057,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <f t="shared" si="9"/>
         <v>395</v>
@@ -3071,7 +3090,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <f t="shared" si="9"/>
         <v>399</v>
@@ -3104,7 +3123,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <f t="shared" si="9"/>
         <v>403</v>
@@ -3137,7 +3156,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <f t="shared" si="9"/>
         <v>407</v>
@@ -3170,7 +3189,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <f t="shared" ref="A82:A89" si="10">A81+5</f>
         <v>412</v>
@@ -3203,7 +3222,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <f t="shared" si="10"/>
         <v>417</v>
@@ -3236,7 +3255,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <f t="shared" si="10"/>
         <v>422</v>
@@ -3269,7 +3288,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
         <f t="shared" si="10"/>
         <v>427</v>
@@ -3302,7 +3321,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
         <f t="shared" si="10"/>
         <v>432</v>
@@ -3335,7 +3354,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
         <f t="shared" si="10"/>
         <v>437</v>
@@ -3368,7 +3387,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <f t="shared" si="10"/>
         <v>442</v>
@@ -3401,7 +3420,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <f t="shared" si="10"/>
         <v>447</v>
@@ -3434,7 +3453,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <f>A89+7</f>
         <v>454</v>
@@ -3467,7 +3486,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <f>A90+7</f>
         <v>461</v>
@@ -3500,7 +3519,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <f>A91+7</f>
         <v>468</v>
@@ -3533,7 +3552,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
         <f>A92+7</f>
         <v>475</v>
@@ -3566,7 +3585,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
         <f t="shared" ref="A94:A103" si="11">A93+10</f>
         <v>485</v>
@@ -3599,7 +3618,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
         <f t="shared" si="11"/>
         <v>495</v>
@@ -3632,7 +3651,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <f t="shared" si="11"/>
         <v>505</v>
@@ -3665,7 +3684,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <f t="shared" si="11"/>
         <v>515</v>
@@ -3698,7 +3717,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <f t="shared" si="11"/>
         <v>525</v>
@@ -3731,7 +3750,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
         <f t="shared" si="11"/>
         <v>535</v>
@@ -3764,7 +3783,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <f t="shared" si="11"/>
         <v>545</v>
@@ -3797,7 +3816,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <f t="shared" si="11"/>
         <v>555</v>
@@ -3830,7 +3849,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
         <f t="shared" si="11"/>
         <v>565</v>
@@ -3863,7 +3882,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <f t="shared" si="11"/>
         <v>575</v>
@@ -3896,7 +3915,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <f t="shared" ref="A104:A113" si="14">A103+20</f>
         <v>595</v>
@@ -3929,7 +3948,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <f t="shared" si="14"/>
         <v>615</v>
@@ -3962,7 +3981,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <f t="shared" si="14"/>
         <v>635</v>
@@ -3995,7 +4014,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
         <f t="shared" si="14"/>
         <v>655</v>
@@ -4028,7 +4047,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <f t="shared" si="14"/>
         <v>675</v>
@@ -4061,7 +4080,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
         <f t="shared" si="14"/>
         <v>695</v>
@@ -4094,7 +4113,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <f t="shared" si="14"/>
         <v>715</v>
@@ -4127,7 +4146,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <f t="shared" si="14"/>
         <v>735</v>
@@ -4160,7 +4179,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <f t="shared" si="14"/>
         <v>755</v>
@@ -4193,7 +4212,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <f t="shared" si="14"/>
         <v>775</v>
@@ -4226,7 +4245,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <f t="shared" ref="A114:A119" si="15">A113+50</f>
         <v>825</v>
@@ -4259,7 +4278,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <f t="shared" si="15"/>
         <v>875</v>
@@ -4292,7 +4311,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <f t="shared" si="15"/>
         <v>925</v>
@@ -4325,7 +4344,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
         <f t="shared" si="15"/>
         <v>975</v>
@@ -4358,7 +4377,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7">
         <f t="shared" si="15"/>
         <v>1025</v>
@@ -4391,7 +4410,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7">
         <f t="shared" si="15"/>
         <v>1075</v>
@@ -4424,7 +4443,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7">
         <f t="shared" ref="A120:A125" si="16">A119+100</f>
         <v>1175</v>
@@ -4457,7 +4476,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
         <f t="shared" si="16"/>
         <v>1275</v>
@@ -4490,7 +4509,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7">
         <f t="shared" si="16"/>
         <v>1375</v>
@@ -4523,7 +4542,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="7">
         <f t="shared" si="16"/>
         <v>1475</v>
@@ -4556,7 +4575,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7">
         <f t="shared" si="16"/>
         <v>1575</v>
@@ -4589,7 +4608,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
         <f t="shared" si="16"/>
         <v>1675</v>
@@ -4622,19 +4641,19 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H126" s="1"/>
     </row>
-    <row r="127" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="8:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="8:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="8:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="8:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H130" s="1"/>
     </row>
   </sheetData>
@@ -4646,17 +4665,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J130"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.5" style="8" customWidth="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
-    <col min="4" max="5" width="12.5" style="8" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" style="8" customWidth="1"/>
-    <col min="8" max="10" width="12.5" style="1" customWidth="1"/>
+    <col min="1" max="2" width="12.44140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="5" width="12.44140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="8" customWidth="1"/>
+    <col min="8" max="10" width="12.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
@@ -4685,7 +4704,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>251</v>
       </c>
@@ -4714,7 +4733,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>252</v>
       </c>
@@ -4743,7 +4762,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>253</v>
       </c>
@@ -4772,7 +4791,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>254</v>
       </c>
@@ -4801,7 +4820,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>255</v>
       </c>
@@ -4830,7 +4849,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>256</v>
       </c>
@@ -4859,7 +4878,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>257</v>
       </c>
@@ -4888,7 +4907,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>258</v>
       </c>
@@ -4917,7 +4936,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>259</v>
       </c>
@@ -4946,7 +4965,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>260</v>
       </c>
@@ -4975,7 +4994,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>261</v>
       </c>
@@ -5004,7 +5023,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>262</v>
       </c>
@@ -5033,7 +5052,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>263</v>
       </c>
@@ -5062,7 +5081,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>264</v>
       </c>
@@ -5091,7 +5110,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>265</v>
       </c>
@@ -5120,7 +5139,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>266</v>
       </c>
@@ -5149,7 +5168,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>267</v>
       </c>
@@ -5178,7 +5197,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>268</v>
       </c>
@@ -5207,7 +5226,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>269</v>
       </c>
@@ -5236,7 +5255,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>270</v>
       </c>
@@ -5265,7 +5284,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>271</v>
       </c>
@@ -5294,7 +5313,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>272</v>
       </c>
@@ -5323,7 +5342,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>273</v>
       </c>
@@ -5352,7 +5371,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>274</v>
       </c>
@@ -5381,7 +5400,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>275</v>
       </c>
@@ -5410,7 +5429,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>276</v>
       </c>
@@ -5439,7 +5458,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>277</v>
       </c>
@@ -5468,7 +5487,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>278</v>
       </c>
@@ -5497,7 +5516,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>279</v>
       </c>
@@ -5526,7 +5545,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>280</v>
       </c>
@@ -5555,7 +5574,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>281</v>
       </c>
@@ -5584,7 +5603,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>282</v>
       </c>
@@ -5613,7 +5632,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>283</v>
       </c>
@@ -5642,7 +5661,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>284</v>
       </c>
@@ -5671,7 +5690,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>286</v>
       </c>
@@ -5700,7 +5719,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>288</v>
       </c>
@@ -5729,7 +5748,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>290</v>
       </c>
@@ -5758,7 +5777,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>292</v>
       </c>
@@ -5787,7 +5806,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>294</v>
       </c>
@@ -5816,7 +5835,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>296</v>
       </c>
@@ -5845,7 +5864,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>299</v>
       </c>
@@ -5874,7 +5893,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>300</v>
       </c>
@@ -5903,7 +5922,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>301</v>
       </c>
@@ -5932,7 +5951,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>302</v>
       </c>
@@ -5961,7 +5980,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>303</v>
       </c>
@@ -5990,7 +6009,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>304</v>
       </c>
@@ -6019,7 +6038,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>305</v>
       </c>
@@ -6048,7 +6067,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>306</v>
       </c>
@@ -6077,7 +6096,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>307</v>
       </c>
@@ -6106,7 +6125,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>308</v>
       </c>
@@ -6135,7 +6154,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>309</v>
       </c>
@@ -6164,7 +6183,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>310</v>
       </c>
@@ -6193,7 +6212,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>311</v>
       </c>
@@ -6222,7 +6241,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>312</v>
       </c>
@@ -6251,7 +6270,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>313</v>
       </c>
@@ -6280,7 +6299,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>314</v>
       </c>
@@ -6309,7 +6328,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>316</v>
       </c>
@@ -6338,7 +6357,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>318</v>
       </c>
@@ -6367,7 +6386,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>320</v>
       </c>
@@ -6396,7 +6415,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>325</v>
       </c>
@@ -6425,7 +6444,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>330</v>
       </c>
@@ -6454,7 +6473,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>335</v>
       </c>
@@ -6480,7 +6499,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>340</v>
       </c>
@@ -6506,7 +6525,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>345</v>
       </c>
@@ -6532,7 +6551,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>350</v>
       </c>
@@ -6558,7 +6577,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>355</v>
       </c>
@@ -6584,7 +6603,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>360</v>
       </c>
@@ -6610,7 +6629,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>365</v>
       </c>
@@ -6636,7 +6655,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>370</v>
       </c>
@@ -6662,7 +6681,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>375</v>
       </c>
@@ -6688,7 +6707,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>380</v>
       </c>
@@ -6714,7 +6733,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>385</v>
       </c>
@@ -6740,7 +6759,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>390</v>
       </c>
@@ -6766,7 +6785,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>395</v>
       </c>
@@ -6792,7 +6811,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>400</v>
       </c>
@@ -6818,7 +6837,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>405</v>
       </c>
@@ -6844,85 +6863,88 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="7">
+    <row r="78" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="12">
         <v>410</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="13">
         <v>816</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="13">
         <v>816</v>
       </c>
-      <c r="E78" s="9">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="F78" s="1">
+      <c r="E78" s="15">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="F78" s="16">
         <v>391.5</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="13">
         <v>404</v>
       </c>
-      <c r="H78" s="9">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="I78" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="7">
+      <c r="H78" s="15">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="I78" s="16">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="J78" s="16"/>
+    </row>
+    <row r="79" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="12">
         <v>415</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="13">
         <v>814</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="13">
         <v>814</v>
       </c>
-      <c r="E79" s="9">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="F79" s="1">
+      <c r="E79" s="15">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="F79" s="16">
         <v>396.5</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="13">
         <v>397</v>
       </c>
-      <c r="H79" s="9">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="I79" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="7">
+      <c r="H79" s="15">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="I79" s="16">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="J79" s="16"/>
+    </row>
+    <row r="80" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="12">
         <v>420</v>
       </c>
-      <c r="B80" s="8">
+      <c r="B80" s="13">
         <v>822</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="13">
         <v>822</v>
       </c>
-      <c r="E80" s="9">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="F80" s="1">
+      <c r="E80" s="15">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="F80" s="16">
         <v>401.5</v>
       </c>
-      <c r="G80" s="8">
+      <c r="G80" s="13">
         <v>400</v>
       </c>
-      <c r="H80" s="9">
-        <v>0.11547005383792516</v>
-      </c>
-      <c r="I80" s="1">
-        <v>0.11547005383792516</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H80" s="15">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="I80" s="16">
+        <v>0.11547005383792516</v>
+      </c>
+      <c r="J80" s="16"/>
+    </row>
+    <row r="81" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>425</v>
       </c>
@@ -6948,7 +6970,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>430</v>
       </c>
@@ -6974,7 +6996,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <v>435</v>
       </c>
@@ -7000,7 +7022,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>440</v>
       </c>
@@ -7026,7 +7048,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
         <v>445</v>
       </c>
@@ -7052,7 +7074,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
         <v>450</v>
       </c>
@@ -7078,7 +7100,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
         <v>460</v>
       </c>
@@ -7104,7 +7126,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>470</v>
       </c>
@@ -7130,7 +7152,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <v>480</v>
       </c>
@@ -7156,7 +7178,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>490</v>
       </c>
@@ -7182,7 +7204,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <v>500</v>
       </c>
@@ -7208,7 +7230,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>510</v>
       </c>
@@ -7234,7 +7256,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
         <v>520</v>
       </c>
@@ -7260,7 +7282,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
         <v>530</v>
       </c>
@@ -7286,7 +7308,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
         <v>540</v>
       </c>
@@ -7312,7 +7334,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>550</v>
       </c>
@@ -7338,7 +7360,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <v>560</v>
       </c>
@@ -7364,7 +7386,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>570</v>
       </c>
@@ -7390,7 +7412,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
         <v>580</v>
       </c>
@@ -7416,7 +7438,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>590</v>
       </c>
@@ -7442,7 +7464,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <v>600</v>
       </c>
@@ -7468,7 +7490,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
         <v>620</v>
       </c>
@@ -7494,7 +7516,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <v>640</v>
       </c>
@@ -7520,7 +7542,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <v>660</v>
       </c>
@@ -7546,7 +7568,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>680</v>
       </c>
@@ -7572,7 +7594,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <v>700</v>
       </c>
@@ -7598,7 +7620,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
         <v>750</v>
       </c>
@@ -7624,7 +7646,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <v>800</v>
       </c>
@@ -7650,7 +7672,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
         <v>850</v>
       </c>
@@ -7676,7 +7698,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <v>900</v>
       </c>
@@ -7702,7 +7724,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <v>1000</v>
       </c>
@@ -7728,7 +7750,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>1100</v>
       </c>
@@ -7754,7 +7776,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <v>1200</v>
       </c>
@@ -7780,7 +7802,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>1300</v>
       </c>
@@ -7806,7 +7828,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <v>1400</v>
       </c>
@@ -7832,7 +7854,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>1500</v>
       </c>
@@ -7858,7 +7880,7 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
         <v>1650</v>
       </c>
@@ -7884,35 +7906,35 @@
         <v>0.11547005383792516</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7"/>
     </row>
-    <row r="119" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7"/>
     </row>
-    <row r="120" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7"/>
     </row>
-    <row r="121" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="7"/>
     </row>
-    <row r="122" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7"/>
     </row>
-    <row r="123" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="7"/>
     </row>
-    <row r="124" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7"/>
     </row>
-    <row r="125" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="7"/>
     </row>
-    <row r="126" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
